--- a/musique.xlsx
+++ b/musique.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6481F0-6CD6-C142-B404-8F238C229FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905011C4-4F80-A84A-98B6-698281C81A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,24 +385,9 @@
     <t>11/12/2025</t>
   </si>
   <si>
-    <t>Jolie Môme (1960)</t>
-  </si>
-  <si>
-    <t>Léo Ferré</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=tqnaPPOWWT4</t>
-  </si>
-  <si>
     <t>12/12/2025</t>
   </si>
   <si>
-    <t>Aerosmith</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=89dGC8de0CA</t>
-  </si>
-  <si>
     <t>15/12/2025</t>
   </si>
   <si>
@@ -1165,9 +1150,6 @@
     <t>Beau-papa (2020)</t>
   </si>
   <si>
-    <t>Dream On (1973)</t>
-  </si>
-  <si>
     <t>Billie Jean (1982)</t>
   </si>
   <si>
@@ -1420,9 +1402,6 @@
     <t>Danses polovtsiennes (1890)</t>
   </si>
   <si>
-    <t>Bamboléo (1978)+B60</t>
-  </si>
-  <si>
     <t>Dans l'antre du roi de la montagne (1875)</t>
   </si>
   <si>
@@ -1757,6 +1736,27 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=GG2jench7Kg&amp;list=RDGG2jench7Kg&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Mistral gagnant (1986)</t>
+  </si>
+  <si>
+    <t>Renaud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_YqzuE-5RE8&amp;list=RD_YqzuE-5RE8&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>ZZ top</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Gg9cNGHl-bg&amp;list=RDGg9cNGHl-bg&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>La grange (1982)</t>
+  </si>
+  <si>
+    <t>Bamboléo (1978)</t>
   </si>
 </sst>
 </file>
@@ -2158,7 +2158,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2201,7 +2201,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2218,16 +2218,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2235,16 +2235,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2252,10 +2252,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C6" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2269,10 +2269,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2286,7 +2286,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2303,7 +2303,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C10" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2337,13 +2337,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C11" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D11" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2371,16 +2371,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2408,7 +2408,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2422,7 +2422,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2439,10 +2439,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2456,10 +2456,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C18" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2499,7 +2499,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2507,13 +2507,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C21" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D21" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2527,7 +2527,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2541,7 +2541,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2558,7 +2558,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2575,7 +2575,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2595,7 +2595,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2609,16 +2609,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C27" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2626,16 +2626,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C28" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="D28" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2643,16 +2643,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2660,16 +2660,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C30" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D30" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2677,16 +2677,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C31" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2694,10 +2694,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C32" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2711,16 +2711,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C33" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2728,16 +2728,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C34" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2745,10 +2745,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C35" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2762,10 +2762,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C36" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2779,16 +2779,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C37" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2796,16 +2796,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C38" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D38" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2813,16 +2813,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C39" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2830,13 +2830,13 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C40" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="D40" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F40" t="s">
         <v>92</v>
@@ -2847,16 +2847,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C41" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2864,16 +2864,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C42" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="D42" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F42" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2881,7 +2881,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2898,7 +2898,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2915,16 +2915,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2938,7 +2938,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2949,16 +2949,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C47" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2966,16 +2966,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C48" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2983,16 +2983,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3017,92 +3017,92 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>567</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>568</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
       </c>
-      <c r="F51" t="s">
-        <v>118</v>
+      <c r="F51" s="1" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>572</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>121</v>
+        <v>571</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C53" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D53" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F53" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>461</v>
+        <v>573</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C55" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="D55" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="F55" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3116,860 +3116,860 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C57" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C59" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s">
         <v>30</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C61" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s">
         <v>15</v>
       </c>
       <c r="F63" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="C64" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D64" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F64" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C65" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C66" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
         <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D68" t="s">
         <v>30</v>
       </c>
       <c r="F68" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C69" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C70" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D71" t="s">
         <v>15</v>
       </c>
       <c r="F71" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C73" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F73" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C74" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="F74" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C75" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B76" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C76" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D76" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
       </c>
       <c r="F77" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B78" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C78" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D79" t="s">
         <v>15</v>
       </c>
       <c r="F79" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B80" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C80" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D80" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F80" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D81" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F81" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C82" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="D82" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="F82" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D83" t="s">
         <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C84" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D84" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F84" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C85" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D85" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F85" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B86" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C86" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C87" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D87" t="s">
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B88" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C88" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B89" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C89" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
       </c>
       <c r="F89" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B90" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C90" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B91" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C91" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D91" t="s">
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B92" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C92" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
       </c>
       <c r="F92" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C93" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
       </c>
       <c r="F93" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B94" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C94" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D94" t="s">
         <v>15</v>
       </c>
       <c r="F94" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B95" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C95" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
       </c>
       <c r="F95" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C96" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D96" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B97" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C97" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B98" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C98" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
         <v>30</v>
       </c>
       <c r="F98" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B99" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C99" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B100" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C100" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
         <v>30</v>
       </c>
       <c r="F100" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B101" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C101" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B102" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C102" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B103" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C103" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
       </c>
       <c r="F103" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B104" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C104" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B105" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C105" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D105" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B106" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
       </c>
       <c r="F106" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B107" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -3978,304 +3978,304 @@
         <v>108</v>
       </c>
       <c r="F107" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B108" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C108" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
       </c>
       <c r="F108" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B109" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B110" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C110" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D110" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F110" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C111" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B112" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C112" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="D112" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F112" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C113" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C114" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D114" t="s">
         <v>15</v>
       </c>
       <c r="F114" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B115" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C115" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B116" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C116" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B117" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C117" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B118" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C118" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B119" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C119" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B120" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C120" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D120" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="F120" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D121" t="s">
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B122" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C122" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D122" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B123" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C123" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
       </c>
       <c r="F123" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B124" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C124" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B125" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -4284,267 +4284,267 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B126" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C126" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B127" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C127" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B128" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C128" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D128" t="s">
         <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B129" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C129" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D129" t="s">
         <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B130" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B131" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C131" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F131" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B132" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="C132" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B133" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C133" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C134" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B135" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C135" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D135" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F135" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B136" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C136" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B137" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C137" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D137" t="s">
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B138" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C138" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D138" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F138" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C140" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D140" t="s">
         <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C141" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D141" t="s">
         <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="C142" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -4563,6 +4563,7 @@
     <hyperlink ref="F105" r:id="rId7" xr:uid="{978C369A-8FBC-F840-B5F4-DF7495B41247}"/>
     <hyperlink ref="F117" r:id="rId8" xr:uid="{15AAE0D8-D438-0445-BD6E-A0C919093326}"/>
     <hyperlink ref="F141" r:id="rId9" xr:uid="{C764D21E-FDB9-1C48-8020-8398498CD7FB}"/>
+    <hyperlink ref="F51" r:id="rId10" xr:uid="{8632FAAB-9942-C948-93C9-135910C1F7F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905011C4-4F80-A84A-98B6-698281C81A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D89CD-E65C-FB40-9B6B-DD54509B08A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="578">
   <si>
     <t>titre</t>
   </si>
@@ -1757,6 +1757,18 @@
   </si>
   <si>
     <t>Bamboléo (1978)</t>
+  </si>
+  <si>
+    <t>Amadou &amp; Mariam</t>
+  </si>
+  <si>
+    <t>Sabali (2010)</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NRtQmqqfdoc&amp;list=RDNRtQmqqfdoc&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -2148,7 +2160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="52.5" customWidth="1"/>
@@ -4545,6 +4557,20 @@
       </c>
       <c r="F142" s="1" t="s">
         <v>529</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>575</v>
+      </c>
+      <c r="C143" t="s">
+        <v>574</v>
+      </c>
+      <c r="D143" t="s">
+        <v>576</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -4564,6 +4590,7 @@
     <hyperlink ref="F117" r:id="rId8" xr:uid="{15AAE0D8-D438-0445-BD6E-A0C919093326}"/>
     <hyperlink ref="F141" r:id="rId9" xr:uid="{C764D21E-FDB9-1C48-8020-8398498CD7FB}"/>
     <hyperlink ref="F51" r:id="rId10" xr:uid="{8632FAAB-9942-C948-93C9-135910C1F7F4}"/>
+    <hyperlink ref="F143" r:id="rId11" xr:uid="{77BCC504-3965-CC42-AD15-C87D59326DF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D89CD-E65C-FB40-9B6B-DD54509B08A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB9D6B8-FE24-F74D-85AD-7707FD383215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="577">
   <si>
     <t>titre</t>
   </si>
@@ -607,12 +607,6 @@
     <t>05/03/2026</t>
   </si>
   <si>
-    <t>Alain Souchon</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=i3bgATxmemc</t>
-  </si>
-  <si>
     <t>06/03/2026</t>
   </si>
   <si>
@@ -1111,9 +1105,6 @@
     <t>Suède</t>
   </si>
   <si>
-    <t>Sous les jupes des filles  (2014)</t>
-  </si>
-  <si>
     <t>YMCA (1978)</t>
   </si>
   <si>
@@ -1769,6 +1760,12 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=NRtQmqqfdoc&amp;list=RDNRtQmqqfdoc&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Dimanche à Bamako (2010)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=O30-zyU-U3M&amp;list=RDO30-zyU-U3M&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -2170,7 +2167,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2196,10 +2193,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2213,7 +2210,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2230,16 +2227,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2247,16 +2244,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2264,10 +2261,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2281,10 +2278,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2298,7 +2295,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2315,7 +2312,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2332,13 +2329,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2349,13 +2346,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2383,16 +2380,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2420,7 +2417,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2434,7 +2431,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2451,10 +2448,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2468,10 +2465,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C18" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2502,7 +2499,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2511,7 +2508,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2519,13 +2516,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2539,7 +2536,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2553,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2570,7 +2567,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2587,7 +2584,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2607,7 +2604,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2621,16 +2618,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C27" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2638,16 +2635,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C28" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D28" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2655,16 +2652,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C29" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2672,16 +2669,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C30" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2689,16 +2686,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C31" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2706,10 +2703,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C32" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2723,16 +2720,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C33" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2740,16 +2737,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C34" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2757,10 +2754,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C35" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2774,10 +2771,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C36" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2791,16 +2788,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C37" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2808,16 +2805,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C38" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2825,16 +2822,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C39" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2842,13 +2839,13 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D40" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F40" t="s">
         <v>92</v>
@@ -2859,16 +2856,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C41" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2876,16 +2873,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C42" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D42" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2893,7 +2890,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2910,7 +2907,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2927,16 +2924,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C45" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2950,7 +2947,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2961,16 +2958,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C47" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2978,16 +2975,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C48" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2995,16 +2992,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C49" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3029,16 +3026,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C51" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3046,16 +3043,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C52" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3063,13 +3060,13 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D53" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -3080,7 +3077,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3097,16 +3094,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C55" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D55" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F55" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3114,7 +3111,7 @@
         <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3131,16 +3128,16 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C57" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3151,7 +3148,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -3165,16 +3162,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C59" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3199,16 +3196,16 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C61" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3250,16 +3247,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D64" t="s">
+        <v>531</v>
+      </c>
+      <c r="F64" t="s">
         <v>532</v>
-      </c>
-      <c r="D64" t="s">
-        <v>534</v>
-      </c>
-      <c r="F64" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3267,16 +3264,16 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C65" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3284,7 +3281,7 @@
         <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C66" t="s">
         <v>145</v>
@@ -3335,16 +3332,16 @@
         <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C69" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3352,16 +3349,16 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C70" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3386,7 +3383,7 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C72" t="s">
         <v>163</v>
@@ -3403,10 +3400,10 @@
         <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C73" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D73" t="s">
         <v>166</v>
@@ -3420,7 +3417,7 @@
         <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C74" t="s">
         <v>169</v>
@@ -3437,16 +3434,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C75" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3454,16 +3451,16 @@
         <v>172</v>
       </c>
       <c r="B76" t="s">
+        <v>430</v>
+      </c>
+      <c r="C76" t="s">
+        <v>431</v>
+      </c>
+      <c r="D76" t="s">
+        <v>432</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C76" t="s">
-        <v>434</v>
-      </c>
-      <c r="D76" t="s">
-        <v>435</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3474,7 +3471,7 @@
         <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3505,7 +3502,7 @@
         <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -3522,16 +3519,16 @@
         <v>183</v>
       </c>
       <c r="B80" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C80" t="s">
+        <v>353</v>
+      </c>
+      <c r="D80" t="s">
         <v>355</v>
       </c>
-      <c r="D80" t="s">
-        <v>357</v>
-      </c>
       <c r="F80" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3542,7 +3539,7 @@
         <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -3556,16 +3553,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C82" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D82" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F82" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3573,143 +3570,143 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>358</v>
+        <v>575</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>571</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>191</v>
+        <v>573</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>190</v>
+      </c>
+      <c r="B84" t="s">
+        <v>434</v>
+      </c>
+      <c r="C84" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" t="s">
         <v>192</v>
       </c>
-      <c r="B84" t="s">
-        <v>437</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="F84" t="s">
         <v>193</v>
-      </c>
-      <c r="D84" t="s">
-        <v>194</v>
-      </c>
-      <c r="F84" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s">
+        <v>459</v>
+      </c>
+      <c r="C85" t="s">
+        <v>195</v>
+      </c>
+      <c r="D85" t="s">
+        <v>390</v>
+      </c>
+      <c r="F85" t="s">
         <v>196</v>
-      </c>
-      <c r="B85" t="s">
-        <v>462</v>
-      </c>
-      <c r="C85" t="s">
-        <v>197</v>
-      </c>
-      <c r="D85" t="s">
-        <v>393</v>
-      </c>
-      <c r="F85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" t="s">
+        <v>382</v>
+      </c>
+      <c r="C87" t="s">
+        <v>201</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
         <v>202</v>
-      </c>
-      <c r="B87" t="s">
-        <v>385</v>
-      </c>
-      <c r="C87" t="s">
-        <v>203</v>
-      </c>
-      <c r="D87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>203</v>
+      </c>
+      <c r="B88" t="s">
+        <v>204</v>
+      </c>
+      <c r="C88" t="s">
         <v>205</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
         <v>206</v>
-      </c>
-      <c r="C88" t="s">
-        <v>207</v>
-      </c>
-      <c r="D88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
       </c>
       <c r="F89" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C91" t="s">
         <v>160</v>
@@ -3718,151 +3715,151 @@
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
+        <v>379</v>
+      </c>
+      <c r="C92" t="s">
+        <v>215</v>
+      </c>
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" t="s">
         <v>216</v>
-      </c>
-      <c r="B92" t="s">
-        <v>382</v>
-      </c>
-      <c r="C92" t="s">
-        <v>217</v>
-      </c>
-      <c r="D92" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C93" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
       </c>
       <c r="F93" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>220</v>
+      </c>
+      <c r="B94" t="s">
+        <v>380</v>
+      </c>
+      <c r="C94" t="s">
+        <v>221</v>
+      </c>
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
         <v>222</v>
-      </c>
-      <c r="B94" t="s">
-        <v>383</v>
-      </c>
-      <c r="C94" t="s">
-        <v>223</v>
-      </c>
-      <c r="D94" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>223</v>
+      </c>
+      <c r="B95" t="s">
+        <v>346</v>
+      </c>
+      <c r="C95" t="s">
+        <v>347</v>
+      </c>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
         <v>225</v>
-      </c>
-      <c r="B95" t="s">
-        <v>348</v>
-      </c>
-      <c r="C95" t="s">
-        <v>349</v>
-      </c>
-      <c r="D95" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" t="s">
+        <v>381</v>
+      </c>
+      <c r="C96" t="s">
+        <v>227</v>
+      </c>
+      <c r="D96" t="s">
         <v>228</v>
       </c>
-      <c r="B96" t="s">
-        <v>384</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="F96" t="s">
         <v>229</v>
-      </c>
-      <c r="D96" t="s">
-        <v>230</v>
-      </c>
-      <c r="F96" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B97" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C97" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>231</v>
+      </c>
+      <c r="B98" t="s">
+        <v>232</v>
+      </c>
+      <c r="C98" t="s">
         <v>233</v>
-      </c>
-      <c r="B98" t="s">
-        <v>234</v>
-      </c>
-      <c r="C98" t="s">
-        <v>235</v>
       </c>
       <c r="D98" t="s">
         <v>30</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B99" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C99" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B100" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C100" t="s">
         <v>131</v>
@@ -3871,32 +3868,32 @@
         <v>30</v>
       </c>
       <c r="F100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>238</v>
+      </c>
+      <c r="B101" t="s">
+        <v>372</v>
+      </c>
+      <c r="C101" t="s">
+        <v>239</v>
+      </c>
+      <c r="D101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
         <v>240</v>
-      </c>
-      <c r="B101" t="s">
-        <v>375</v>
-      </c>
-      <c r="C101" t="s">
-        <v>241</v>
-      </c>
-      <c r="D101" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C102" t="s">
         <v>149</v>
@@ -3905,83 +3902,83 @@
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>244</v>
+      </c>
+      <c r="B103" t="s">
+        <v>245</v>
+      </c>
+      <c r="C103" t="s">
         <v>246</v>
       </c>
-      <c r="B103" t="s">
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" t="s">
         <v>247</v>
-      </c>
-      <c r="C103" t="s">
-        <v>248</v>
-      </c>
-      <c r="D103" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B104" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C104" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B105" t="s">
+        <v>435</v>
+      </c>
+      <c r="C105" t="s">
+        <v>436</v>
+      </c>
+      <c r="D105" t="s">
+        <v>437</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C105" t="s">
-        <v>439</v>
-      </c>
-      <c r="D105" t="s">
-        <v>440</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>251</v>
+      </c>
+      <c r="B106" t="s">
+        <v>357</v>
+      </c>
+      <c r="C106" t="s">
+        <v>252</v>
+      </c>
+      <c r="D106" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" t="s">
         <v>253</v>
-      </c>
-      <c r="B106" t="s">
-        <v>360</v>
-      </c>
-      <c r="C106" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B107" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -3990,304 +3987,304 @@
         <v>108</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" t="s">
+        <v>383</v>
+      </c>
+      <c r="C108" t="s">
+        <v>257</v>
+      </c>
+      <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
         <v>258</v>
-      </c>
-      <c r="B108" t="s">
-        <v>386</v>
-      </c>
-      <c r="C108" t="s">
-        <v>259</v>
-      </c>
-      <c r="D108" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>259</v>
+      </c>
+      <c r="B109" t="s">
+        <v>260</v>
+      </c>
+      <c r="C109" t="s">
+        <v>341</v>
+      </c>
+      <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" t="s">
         <v>261</v>
-      </c>
-      <c r="B109" t="s">
-        <v>262</v>
-      </c>
-      <c r="C109" t="s">
-        <v>343</v>
-      </c>
-      <c r="D109" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B110" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C110" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D110" t="s">
         <v>166</v>
       </c>
       <c r="F110" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B111" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B112" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C112" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D112" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F112" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B113" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C113" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>271</v>
+      </c>
+      <c r="B114" t="s">
+        <v>360</v>
+      </c>
+      <c r="C114" t="s">
+        <v>272</v>
+      </c>
+      <c r="D114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" t="s">
         <v>273</v>
-      </c>
-      <c r="B114" t="s">
-        <v>363</v>
-      </c>
-      <c r="C114" t="s">
-        <v>274</v>
-      </c>
-      <c r="D114" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>274</v>
+      </c>
+      <c r="B115" t="s">
+        <v>275</v>
+      </c>
+      <c r="C115" t="s">
         <v>276</v>
       </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" t="s">
         <v>277</v>
-      </c>
-      <c r="C115" t="s">
-        <v>278</v>
-      </c>
-      <c r="D115" t="s">
-        <v>15</v>
-      </c>
-      <c r="F115" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B116" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C116" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B117" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>280</v>
+      </c>
+      <c r="B118" t="s">
+        <v>281</v>
+      </c>
+      <c r="C118" t="s">
+        <v>391</v>
+      </c>
+      <c r="D118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" t="s">
         <v>282</v>
-      </c>
-      <c r="B118" t="s">
-        <v>283</v>
-      </c>
-      <c r="C118" t="s">
-        <v>394</v>
-      </c>
-      <c r="D118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B119" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C119" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B120" t="s">
+        <v>416</v>
+      </c>
+      <c r="C120" t="s">
+        <v>417</v>
+      </c>
+      <c r="D120" t="s">
+        <v>418</v>
+      </c>
+      <c r="F120" t="s">
         <v>419</v>
-      </c>
-      <c r="C120" t="s">
-        <v>420</v>
-      </c>
-      <c r="D120" t="s">
-        <v>421</v>
-      </c>
-      <c r="F120" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>286</v>
+      </c>
+      <c r="B121" t="s">
+        <v>287</v>
+      </c>
+      <c r="C121" t="s">
         <v>288</v>
       </c>
-      <c r="B121" t="s">
+      <c r="D121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
         <v>289</v>
-      </c>
-      <c r="C121" t="s">
-        <v>290</v>
-      </c>
-      <c r="D121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>290</v>
+      </c>
+      <c r="B122" t="s">
+        <v>361</v>
+      </c>
+      <c r="C122" t="s">
+        <v>291</v>
+      </c>
+      <c r="D122" t="s">
         <v>292</v>
       </c>
-      <c r="B122" t="s">
-        <v>364</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="F122" t="s">
         <v>293</v>
-      </c>
-      <c r="D122" t="s">
-        <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C123" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
       </c>
       <c r="F123" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>297</v>
+      </c>
+      <c r="B124" t="s">
+        <v>298</v>
+      </c>
+      <c r="C124" t="s">
         <v>299</v>
-      </c>
-      <c r="B124" t="s">
-        <v>300</v>
-      </c>
-      <c r="C124" t="s">
-        <v>301</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B125" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -4296,83 +4293,83 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>304</v>
+      </c>
+      <c r="B126" t="s">
+        <v>305</v>
+      </c>
+      <c r="C126" t="s">
         <v>306</v>
-      </c>
-      <c r="B126" t="s">
-        <v>307</v>
-      </c>
-      <c r="C126" t="s">
-        <v>308</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C127" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>309</v>
+      </c>
+      <c r="B128" t="s">
+        <v>310</v>
+      </c>
+      <c r="C128" t="s">
         <v>311</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>312</v>
-      </c>
-      <c r="C128" t="s">
-        <v>313</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B129" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C129" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D129" t="s">
         <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B130" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -4381,117 +4378,117 @@
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B131" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C131" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F131" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B132" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C132" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B133" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C133" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>321</v>
+      </c>
+      <c r="B134" t="s">
+        <v>322</v>
+      </c>
+      <c r="C134" t="s">
         <v>323</v>
-      </c>
-      <c r="B134" t="s">
-        <v>324</v>
-      </c>
-      <c r="C134" t="s">
-        <v>325</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B135" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C135" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D135" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F135" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B136" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C136" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B137" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -4500,77 +4497,77 @@
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B138" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C138" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D138" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F138" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C140" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D140" t="s">
         <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C141" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D141" t="s">
         <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C142" t="s">
+        <v>523</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C143" t="s">
+        <v>571</v>
+      </c>
+      <c r="D143" t="s">
+        <v>573</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D143" t="s">
-        <v>576</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB9D6B8-FE24-F74D-85AD-7707FD383215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F596DD-BD2B-9E4D-B4DF-CB1221F4AE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="572">
   <si>
     <t>titre</t>
   </si>
@@ -862,15 +862,6 @@
     <t>22/05/2026</t>
   </si>
   <si>
-    <t>Sur la planche (2011)</t>
-  </si>
-  <si>
-    <t>La Femme</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=NwVA5zYfNWw</t>
-  </si>
-  <si>
     <t>26/05/2026</t>
   </si>
   <si>
@@ -1753,13 +1744,7 @@
     <t>Amadou &amp; Mariam</t>
   </si>
   <si>
-    <t>Sabali (2010)</t>
-  </si>
-  <si>
     <t>Mali</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=NRtQmqqfdoc&amp;list=RDNRtQmqqfdoc&amp;start_radio=1</t>
   </si>
   <si>
     <t>Dimanche à Bamako (2010)</t>
@@ -2157,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="52.5" customWidth="1"/>
@@ -2167,7 +2152,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2193,10 +2178,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2210,7 +2195,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2227,16 +2212,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2244,16 +2229,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2261,10 +2246,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2278,10 +2263,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2295,7 +2280,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2312,7 +2297,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2329,13 +2314,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C10" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2346,13 +2331,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2380,16 +2365,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2417,7 +2402,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2431,7 +2416,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2448,10 +2433,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C17" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2465,10 +2450,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2499,7 +2484,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2508,7 +2493,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2516,13 +2501,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C21" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D21" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2536,7 +2521,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2550,7 +2535,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2567,7 +2552,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2584,7 +2569,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2604,7 +2589,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2618,16 +2603,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C27" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2635,16 +2620,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C28" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2652,16 +2637,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C29" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2669,16 +2654,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C30" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2686,16 +2671,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C31" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2703,10 +2688,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C32" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2720,16 +2705,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C33" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2737,16 +2722,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C34" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2754,10 +2739,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2771,10 +2756,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2788,16 +2773,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C37" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2805,16 +2790,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C38" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D38" t="s">
         <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2822,16 +2807,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C39" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2839,10 +2824,10 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C40" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D40" t="s">
         <v>268</v>
@@ -2856,16 +2841,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C41" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2873,16 +2858,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C42" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D42" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2890,7 +2875,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2907,7 +2892,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2924,16 +2909,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C45" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2947,7 +2932,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2958,16 +2943,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C47" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2975,16 +2960,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C48" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2992,16 +2977,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C49" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3026,16 +3011,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C51" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3043,16 +3028,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C52" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3060,13 +3045,13 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C53" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D53" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -3077,7 +3062,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3094,16 +3079,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C55" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D55" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F55" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3111,7 +3096,7 @@
         <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3128,16 +3113,16 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C57" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3148,7 +3133,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -3162,16 +3147,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C59" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3196,16 +3181,16 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C61" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3247,16 +3232,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C64" t="s">
+        <v>526</v>
+      </c>
+      <c r="D64" t="s">
+        <v>528</v>
+      </c>
+      <c r="F64" t="s">
         <v>529</v>
-      </c>
-      <c r="D64" t="s">
-        <v>531</v>
-      </c>
-      <c r="F64" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3264,16 +3249,16 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C65" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3281,7 +3266,7 @@
         <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C66" t="s">
         <v>145</v>
@@ -3332,16 +3317,16 @@
         <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C69" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3349,16 +3334,16 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C70" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3383,7 +3368,7 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C72" t="s">
         <v>163</v>
@@ -3400,10 +3385,10 @@
         <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C73" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D73" t="s">
         <v>166</v>
@@ -3417,7 +3402,7 @@
         <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C74" t="s">
         <v>169</v>
@@ -3434,16 +3419,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C75" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3451,16 +3436,16 @@
         <v>172</v>
       </c>
       <c r="B76" t="s">
+        <v>427</v>
+      </c>
+      <c r="C76" t="s">
+        <v>428</v>
+      </c>
+      <c r="D76" t="s">
+        <v>429</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C76" t="s">
-        <v>431</v>
-      </c>
-      <c r="D76" t="s">
-        <v>432</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3471,7 +3456,7 @@
         <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3502,7 +3487,7 @@
         <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -3519,16 +3504,16 @@
         <v>183</v>
       </c>
       <c r="B80" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C80" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D80" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F80" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3539,7 +3524,7 @@
         <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -3553,16 +3538,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C82" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D82" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F82" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3570,16 +3555,16 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C83" t="s">
+        <v>568</v>
+      </c>
+      <c r="D83" t="s">
+        <v>569</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="D83" t="s">
-        <v>573</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3587,7 +3572,7 @@
         <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C84" t="s">
         <v>191</v>
@@ -3604,13 +3589,13 @@
         <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C85" t="s">
         <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F85" t="s">
         <v>196</v>
@@ -3621,7 +3606,7 @@
         <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C86" t="s">
         <v>198</v>
@@ -3638,7 +3623,7 @@
         <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C87" t="s">
         <v>201</v>
@@ -3672,10 +3657,10 @@
         <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C89" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
@@ -3689,7 +3674,7 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C90" t="s">
         <v>210</v>
@@ -3706,7 +3691,7 @@
         <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C91" t="s">
         <v>160</v>
@@ -3723,7 +3708,7 @@
         <v>214</v>
       </c>
       <c r="B92" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C92" t="s">
         <v>215</v>
@@ -3743,7 +3728,7 @@
         <v>218</v>
       </c>
       <c r="C93" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
@@ -3757,7 +3742,7 @@
         <v>220</v>
       </c>
       <c r="B94" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C94" t="s">
         <v>221</v>
@@ -3774,10 +3759,10 @@
         <v>223</v>
       </c>
       <c r="B95" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C95" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -3791,7 +3776,7 @@
         <v>226</v>
       </c>
       <c r="B96" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C96" t="s">
         <v>227</v>
@@ -3808,16 +3793,16 @@
         <v>230</v>
       </c>
       <c r="B97" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C97" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -3842,16 +3827,16 @@
         <v>235</v>
       </c>
       <c r="B99" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C99" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
@@ -3859,7 +3844,7 @@
         <v>236</v>
       </c>
       <c r="B100" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C100" t="s">
         <v>131</v>
@@ -3876,7 +3861,7 @@
         <v>238</v>
       </c>
       <c r="B101" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C101" t="s">
         <v>239</v>
@@ -3927,10 +3912,10 @@
         <v>248</v>
       </c>
       <c r="B104" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C104" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
@@ -3944,16 +3929,16 @@
         <v>250</v>
       </c>
       <c r="B105" t="s">
+        <v>432</v>
+      </c>
+      <c r="C105" t="s">
+        <v>433</v>
+      </c>
+      <c r="D105" t="s">
+        <v>434</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C105" t="s">
-        <v>436</v>
-      </c>
-      <c r="D105" t="s">
-        <v>437</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -3961,7 +3946,7 @@
         <v>251</v>
       </c>
       <c r="B106" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C106" t="s">
         <v>252</v>
@@ -3978,7 +3963,7 @@
         <v>254</v>
       </c>
       <c r="B107" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -3995,7 +3980,7 @@
         <v>256</v>
       </c>
       <c r="B108" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C108" t="s">
         <v>257</v>
@@ -4015,7 +4000,7 @@
         <v>260</v>
       </c>
       <c r="C109" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -4029,10 +4014,10 @@
         <v>262</v>
       </c>
       <c r="B110" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C110" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D110" t="s">
         <v>166</v>
@@ -4049,7 +4034,7 @@
         <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -4063,16 +4048,16 @@
         <v>267</v>
       </c>
       <c r="B112" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C112" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D112" t="s">
         <v>268</v>
       </c>
       <c r="F112" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -4080,7 +4065,7 @@
         <v>269</v>
       </c>
       <c r="B113" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C113" t="s">
         <v>205</v>
@@ -4097,7 +4082,7 @@
         <v>271</v>
       </c>
       <c r="B114" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C114" t="s">
         <v>272</v>
@@ -4114,177 +4099,177 @@
         <v>274</v>
       </c>
       <c r="B115" t="s">
-        <v>275</v>
+        <v>516</v>
       </c>
       <c r="C115" t="s">
-        <v>276</v>
+        <v>515</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>514</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B116" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C116" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C117" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B118" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C118" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B119" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B120" t="s">
+        <v>413</v>
+      </c>
+      <c r="C120" t="s">
+        <v>414</v>
+      </c>
+      <c r="D120" t="s">
+        <v>415</v>
+      </c>
+      <c r="F120" t="s">
         <v>416</v>
-      </c>
-      <c r="C120" t="s">
-        <v>417</v>
-      </c>
-      <c r="D120" t="s">
-        <v>418</v>
-      </c>
-      <c r="F120" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" t="s">
+        <v>285</v>
+      </c>
+      <c r="D121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
         <v>286</v>
-      </c>
-      <c r="B121" t="s">
-        <v>287</v>
-      </c>
-      <c r="C121" t="s">
-        <v>288</v>
-      </c>
-      <c r="D121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>287</v>
+      </c>
+      <c r="B122" t="s">
+        <v>358</v>
+      </c>
+      <c r="C122" t="s">
+        <v>288</v>
+      </c>
+      <c r="D122" t="s">
+        <v>289</v>
+      </c>
+      <c r="F122" t="s">
         <v>290</v>
-      </c>
-      <c r="B122" t="s">
-        <v>361</v>
-      </c>
-      <c r="C122" t="s">
-        <v>291</v>
-      </c>
-      <c r="D122" t="s">
-        <v>292</v>
-      </c>
-      <c r="F122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C123" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
       </c>
       <c r="F123" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B124" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C124" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -4293,83 +4278,83 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B126" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C126" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B127" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C127" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>306</v>
+      </c>
+      <c r="B128" t="s">
+        <v>307</v>
+      </c>
+      <c r="C128" t="s">
+        <v>308</v>
+      </c>
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>309</v>
-      </c>
-      <c r="B128" t="s">
-        <v>310</v>
-      </c>
-      <c r="C128" t="s">
-        <v>311</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B129" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C129" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D129" t="s">
         <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B130" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -4378,117 +4363,117 @@
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B131" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C131" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D131" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F131" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B132" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C132" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B133" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C133" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B134" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C134" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B135" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C135" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D135" t="s">
         <v>224</v>
       </c>
       <c r="F135" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B136" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B137" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -4497,38 +4482,38 @@
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B138" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C138" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D138" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F138" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
+        <v>518</v>
+      </c>
+      <c r="C140" t="s">
+        <v>517</v>
+      </c>
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="C140" t="s">
-        <v>518</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
@@ -4538,36 +4523,8 @@
       <c r="C141" t="s">
         <v>520</v>
       </c>
-      <c r="D141" t="s">
-        <v>15</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B142" t="s">
-        <v>524</v>
-      </c>
-      <c r="C142" t="s">
         <v>523</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B143" t="s">
-        <v>572</v>
-      </c>
-      <c r="C143" t="s">
-        <v>571</v>
-      </c>
-      <c r="D143" t="s">
-        <v>573</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -4585,9 +4542,8 @@
     <hyperlink ref="F76" r:id="rId6" xr:uid="{B14F8477-D0F1-4540-BA6D-C5FE9DDFE1AD}"/>
     <hyperlink ref="F105" r:id="rId7" xr:uid="{978C369A-8FBC-F840-B5F4-DF7495B41247}"/>
     <hyperlink ref="F117" r:id="rId8" xr:uid="{15AAE0D8-D438-0445-BD6E-A0C919093326}"/>
-    <hyperlink ref="F141" r:id="rId9" xr:uid="{C764D21E-FDB9-1C48-8020-8398498CD7FB}"/>
+    <hyperlink ref="F140" r:id="rId9" xr:uid="{C764D21E-FDB9-1C48-8020-8398498CD7FB}"/>
     <hyperlink ref="F51" r:id="rId10" xr:uid="{8632FAAB-9942-C948-93C9-135910C1F7F4}"/>
-    <hyperlink ref="F143" r:id="rId11" xr:uid="{77BCC504-3965-CC42-AD15-C87D59326DF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F596DD-BD2B-9E4D-B4DF-CB1221F4AE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C17CCB-ADBF-4347-A94C-859A5D37A7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="574">
   <si>
     <t>titre</t>
   </si>
@@ -1751,6 +1751,12 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=O30-zyU-U3M&amp;list=RDO30-zyU-U3M&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>Cuba</t>
   </si>
 </sst>
 </file>
@@ -3612,7 +3618,7 @@
         <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>573</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
@@ -4503,6 +4509,9 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>572</v>
+      </c>
       <c r="B140" t="s">
         <v>518</v>
       </c>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C17CCB-ADBF-4347-A94C-859A5D37A7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C84761-B512-B440-B547-62374998B14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="579">
   <si>
     <t>titre</t>
   </si>
@@ -676,9 +676,6 @@
     <t>19/03/2026</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=V6gjzNm6dA0</t>
-  </si>
-  <si>
     <t>20/03/2026</t>
   </si>
   <si>
@@ -1162,9 +1159,6 @@
     <t>La Traviata (1853)</t>
   </si>
   <si>
-    <t>La Javanaise (1963)</t>
-  </si>
-  <si>
     <t>Christine (2014)</t>
   </si>
   <si>
@@ -1757,6 +1751,28 @@
   </si>
   <si>
     <t>Cuba</t>
+  </si>
+  <si>
+    <t>Mayra Andrade</t>
+  </si>
+  <si>
+    <t>Comme s' il en pleuvait (2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Cap-Vert</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rL9QXx2pvio&amp;list=RDrL9QXx2pvio&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Manu Dibango</t>
+  </si>
+  <si>
+    <t>Cameroun</t>
+  </si>
+  <si>
+    <t>Soul Makossa (1972)</t>
   </si>
 </sst>
 </file>
@@ -2148,7 +2164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="52.5" customWidth="1"/>
@@ -2158,7 +2174,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2184,10 +2200,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2201,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2218,16 +2234,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" t="s">
         <v>395</v>
-      </c>
-      <c r="C4" t="s">
-        <v>397</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2235,16 +2251,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>410</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2252,10 +2268,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2269,10 +2285,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2286,7 +2302,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2303,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2320,13 +2336,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2337,13 +2353,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D11" t="s">
         <v>335</v>
-      </c>
-      <c r="D11" t="s">
-        <v>336</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2371,16 +2387,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2408,7 +2424,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2422,7 +2438,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2439,10 +2455,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2456,10 +2472,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2490,7 +2506,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2499,7 +2515,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2507,13 +2523,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C21" t="s">
+        <v>332</v>
+      </c>
+      <c r="D21" t="s">
         <v>333</v>
-      </c>
-      <c r="D21" t="s">
-        <v>334</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2527,7 +2543,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2541,7 +2557,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2558,7 +2574,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2575,7 +2591,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2595,7 +2611,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2609,16 +2625,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C27" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2626,16 +2642,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C28" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D28" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2643,16 +2659,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C29" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2660,16 +2676,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C30" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2677,16 +2693,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2694,10 +2710,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" t="s">
         <v>339</v>
-      </c>
-      <c r="C32" t="s">
-        <v>340</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2711,16 +2727,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C33" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2728,16 +2744,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2745,10 +2761,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2762,10 +2778,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2779,16 +2795,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C37" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2796,16 +2812,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C38" t="s">
+        <v>421</v>
+      </c>
+      <c r="D38" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" t="s">
         <v>423</v>
-      </c>
-      <c r="D38" t="s">
-        <v>228</v>
-      </c>
-      <c r="F38" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2813,16 +2829,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C39" t="s">
+        <v>405</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>406</v>
-      </c>
-      <c r="C39" t="s">
-        <v>407</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2830,13 +2846,13 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C40" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F40" t="s">
         <v>92</v>
@@ -2847,16 +2863,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C41" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2864,16 +2880,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C42" t="s">
+        <v>488</v>
+      </c>
+      <c r="D42" t="s">
+        <v>489</v>
+      </c>
+      <c r="F42" t="s">
         <v>490</v>
-      </c>
-      <c r="D42" t="s">
-        <v>491</v>
-      </c>
-      <c r="F42" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2881,7 +2897,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2898,7 +2914,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2915,16 +2931,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C45" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2938,7 +2954,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2949,16 +2965,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C47" t="s">
+        <v>492</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>494</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2966,16 +2982,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C48" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2983,16 +2999,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C49" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3017,16 +3033,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
+        <v>559</v>
+      </c>
+      <c r="C51" t="s">
+        <v>560</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C51" t="s">
-        <v>562</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3034,16 +3050,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C52" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3051,13 +3067,13 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C53" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D53" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -3068,7 +3084,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3085,16 +3101,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C55" t="s">
+        <v>497</v>
+      </c>
+      <c r="D55" t="s">
         <v>499</v>
       </c>
-      <c r="D55" t="s">
-        <v>501</v>
-      </c>
       <c r="F55" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3102,7 +3118,7 @@
         <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3119,16 +3135,16 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C57" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3139,7 +3155,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -3153,16 +3169,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C59" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3187,16 +3203,16 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C61" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3238,16 +3254,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
+        <v>525</v>
+      </c>
+      <c r="C64" t="s">
+        <v>524</v>
+      </c>
+      <c r="D64" t="s">
+        <v>526</v>
+      </c>
+      <c r="F64" t="s">
         <v>527</v>
-      </c>
-      <c r="C64" t="s">
-        <v>526</v>
-      </c>
-      <c r="D64" t="s">
-        <v>528</v>
-      </c>
-      <c r="F64" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3255,16 +3271,16 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C65" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3272,7 +3288,7 @@
         <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C66" t="s">
         <v>145</v>
@@ -3323,16 +3339,16 @@
         <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C69" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3340,16 +3356,16 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C70" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3374,7 +3390,7 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C72" t="s">
         <v>163</v>
@@ -3391,10 +3407,10 @@
         <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C73" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D73" t="s">
         <v>166</v>
@@ -3408,7 +3424,7 @@
         <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C74" t="s">
         <v>169</v>
@@ -3425,16 +3441,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C75" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3442,16 +3458,16 @@
         <v>172</v>
       </c>
       <c r="B76" t="s">
+        <v>425</v>
+      </c>
+      <c r="C76" t="s">
+        <v>426</v>
+      </c>
+      <c r="D76" t="s">
         <v>427</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="D76" t="s">
-        <v>429</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3462,7 +3478,7 @@
         <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3493,7 +3509,7 @@
         <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -3510,16 +3526,16 @@
         <v>183</v>
       </c>
       <c r="B80" t="s">
+        <v>350</v>
+      </c>
+      <c r="C80" t="s">
+        <v>349</v>
+      </c>
+      <c r="D80" t="s">
         <v>351</v>
       </c>
-      <c r="C80" t="s">
-        <v>350</v>
-      </c>
-      <c r="D80" t="s">
-        <v>352</v>
-      </c>
       <c r="F80" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3530,7 +3546,7 @@
         <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -3544,16 +3560,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C82" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D82" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F82" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3561,16 +3577,16 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C83" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3578,7 +3594,7 @@
         <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C84" t="s">
         <v>191</v>
@@ -3595,13 +3611,13 @@
         <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C85" t="s">
         <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F85" t="s">
         <v>196</v>
@@ -3612,13 +3628,13 @@
         <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C86" t="s">
         <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
@@ -3629,7 +3645,7 @@
         <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C87" t="s">
         <v>201</v>
@@ -3663,10 +3679,10 @@
         <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C89" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
@@ -3680,7 +3696,7 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C90" t="s">
         <v>210</v>
@@ -3692,165 +3708,165 @@
         <v>211</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>375</v>
+        <v>573</v>
       </c>
       <c r="C91" t="s">
-        <v>160</v>
-      </c>
-      <c r="D91" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" t="s">
-        <v>213</v>
+        <v>572</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>213</v>
+      </c>
+      <c r="B92" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" t="s">
         <v>214</v>
       </c>
-      <c r="B92" t="s">
-        <v>376</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" t="s">
         <v>215</v>
-      </c>
-      <c r="D92" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
         <v>217</v>
       </c>
-      <c r="B93" t="s">
-        <v>218</v>
-      </c>
       <c r="C93" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
       </c>
       <c r="F93" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" t="s">
+        <v>375</v>
+      </c>
+      <c r="C94" t="s">
         <v>220</v>
       </c>
-      <c r="B94" t="s">
-        <v>377</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
         <v>221</v>
-      </c>
-      <c r="D94" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B95" t="s">
+        <v>342</v>
+      </c>
+      <c r="C95" t="s">
         <v>343</v>
       </c>
-      <c r="C95" t="s">
-        <v>344</v>
-      </c>
       <c r="D95" t="s">
         <v>15</v>
       </c>
       <c r="F95" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>225</v>
+      </c>
+      <c r="B96" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" t="s">
         <v>226</v>
       </c>
-      <c r="B96" t="s">
-        <v>378</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>227</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>228</v>
-      </c>
-      <c r="F96" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C97" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>230</v>
+      </c>
+      <c r="B98" t="s">
         <v>231</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>232</v>
-      </c>
-      <c r="C98" t="s">
-        <v>233</v>
       </c>
       <c r="D98" t="s">
         <v>30</v>
       </c>
       <c r="F98" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B99" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C99" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C100" t="s">
         <v>131</v>
@@ -3859,32 +3875,32 @@
         <v>30</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>237</v>
+      </c>
+      <c r="B101" t="s">
+        <v>368</v>
+      </c>
+      <c r="C101" t="s">
         <v>238</v>
       </c>
-      <c r="B101" t="s">
-        <v>369</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
         <v>239</v>
-      </c>
-      <c r="D101" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>240</v>
+      </c>
+      <c r="B102" t="s">
         <v>241</v>
-      </c>
-      <c r="B102" t="s">
-        <v>242</v>
       </c>
       <c r="C102" t="s">
         <v>149</v>
@@ -3893,83 +3909,83 @@
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>243</v>
+      </c>
+      <c r="B103" t="s">
         <v>244</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>245</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" t="s">
         <v>246</v>
-      </c>
-      <c r="D103" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B104" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C104" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B105" t="s">
+        <v>430</v>
+      </c>
+      <c r="C105" t="s">
+        <v>431</v>
+      </c>
+      <c r="D105" t="s">
         <v>432</v>
       </c>
-      <c r="C105" t="s">
+      <c r="F105" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="D105" t="s">
-        <v>434</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>250</v>
+      </c>
+      <c r="B106" t="s">
+        <v>353</v>
+      </c>
+      <c r="C106" t="s">
         <v>251</v>
       </c>
-      <c r="B106" t="s">
-        <v>354</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" t="s">
         <v>252</v>
-      </c>
-      <c r="D106" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -3978,100 +3994,100 @@
         <v>108</v>
       </c>
       <c r="F107" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>255</v>
+      </c>
+      <c r="B108" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" t="s">
         <v>256</v>
       </c>
-      <c r="B108" t="s">
-        <v>380</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
         <v>257</v>
-      </c>
-      <c r="D108" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>258</v>
+      </c>
+      <c r="B109" t="s">
         <v>259</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
+        <v>337</v>
+      </c>
+      <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" t="s">
         <v>260</v>
-      </c>
-      <c r="C109" t="s">
-        <v>338</v>
-      </c>
-      <c r="D109" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B110" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C110" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D110" t="s">
         <v>166</v>
       </c>
       <c r="F110" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>263</v>
+      </c>
+      <c r="B111" t="s">
         <v>264</v>
       </c>
-      <c r="B111" t="s">
-        <v>265</v>
-      </c>
       <c r="C111" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>266</v>
+      </c>
+      <c r="B112" t="s">
+        <v>445</v>
+      </c>
+      <c r="C112" t="s">
+        <v>476</v>
+      </c>
+      <c r="D112" t="s">
         <v>267</v>
       </c>
-      <c r="B112" t="s">
-        <v>447</v>
-      </c>
-      <c r="C112" t="s">
-        <v>478</v>
-      </c>
-      <c r="D112" t="s">
-        <v>268</v>
-      </c>
       <c r="F112" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B113" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C113" t="s">
         <v>205</v>
@@ -4080,202 +4096,202 @@
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>270</v>
+      </c>
+      <c r="B114" t="s">
+        <v>356</v>
+      </c>
+      <c r="C114" t="s">
         <v>271</v>
       </c>
-      <c r="B114" t="s">
-        <v>357</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" t="s">
         <v>272</v>
-      </c>
-      <c r="D114" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C115" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C116" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
+        <v>434</v>
+      </c>
+      <c r="C117" t="s">
         <v>436</v>
-      </c>
-      <c r="C117" t="s">
-        <v>438</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>276</v>
+      </c>
+      <c r="B118" t="s">
         <v>277</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
+        <v>386</v>
+      </c>
+      <c r="D118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" t="s">
         <v>278</v>
-      </c>
-      <c r="C118" t="s">
-        <v>388</v>
-      </c>
-      <c r="D118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>279</v>
+      </c>
+      <c r="B119" t="s">
         <v>280</v>
       </c>
-      <c r="B119" t="s">
-        <v>281</v>
-      </c>
       <c r="C119" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B120" t="s">
+        <v>411</v>
+      </c>
+      <c r="C120" t="s">
+        <v>412</v>
+      </c>
+      <c r="D120" t="s">
         <v>413</v>
       </c>
-      <c r="C120" t="s">
+      <c r="F120" t="s">
         <v>414</v>
-      </c>
-      <c r="D120" t="s">
-        <v>415</v>
-      </c>
-      <c r="F120" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>282</v>
+      </c>
+      <c r="B121" t="s">
         <v>283</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>284</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
         <v>285</v>
-      </c>
-      <c r="D121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>286</v>
+      </c>
+      <c r="B122" t="s">
+        <v>357</v>
+      </c>
+      <c r="C122" t="s">
         <v>287</v>
       </c>
-      <c r="B122" t="s">
-        <v>358</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>288</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>289</v>
-      </c>
-      <c r="F122" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>290</v>
+      </c>
+      <c r="B123" t="s">
         <v>291</v>
       </c>
-      <c r="B123" t="s">
-        <v>292</v>
-      </c>
       <c r="C123" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
       </c>
       <c r="F123" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>293</v>
+      </c>
+      <c r="B124" t="s">
         <v>294</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>295</v>
-      </c>
-      <c r="C124" t="s">
-        <v>296</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>297</v>
+      </c>
+      <c r="B125" t="s">
         <v>298</v>
-      </c>
-      <c r="B125" t="s">
-        <v>299</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -4284,83 +4300,83 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>300</v>
+      </c>
+      <c r="B126" t="s">
         <v>301</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>302</v>
-      </c>
-      <c r="C126" t="s">
-        <v>303</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B127" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C127" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>305</v>
+      </c>
+      <c r="B128" t="s">
         <v>306</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>307</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B129" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C129" t="s">
+        <v>509</v>
+      </c>
+      <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" t="s">
         <v>511</v>
-      </c>
-      <c r="D129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>310</v>
+      </c>
+      <c r="B130" t="s">
         <v>311</v>
-      </c>
-      <c r="B130" t="s">
-        <v>312</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -4369,117 +4385,117 @@
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>313</v>
+      </c>
+      <c r="B131" t="s">
+        <v>446</v>
+      </c>
+      <c r="C131" t="s">
+        <v>480</v>
+      </c>
+      <c r="D131" t="s">
+        <v>385</v>
+      </c>
+      <c r="F131" t="s">
         <v>314</v>
-      </c>
-      <c r="B131" t="s">
-        <v>448</v>
-      </c>
-      <c r="C131" t="s">
-        <v>482</v>
-      </c>
-      <c r="D131" t="s">
-        <v>387</v>
-      </c>
-      <c r="F131" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B132" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C132" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B133" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C133" t="s">
+        <v>528</v>
+      </c>
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" t="s">
         <v>530</v>
-      </c>
-      <c r="D133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>317</v>
+      </c>
+      <c r="B134" t="s">
         <v>318</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>319</v>
-      </c>
-      <c r="C134" t="s">
-        <v>320</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>321</v>
+      </c>
+      <c r="B135" t="s">
         <v>322</v>
       </c>
-      <c r="B135" t="s">
-        <v>323</v>
-      </c>
       <c r="C135" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D135" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F135" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>323</v>
+      </c>
+      <c r="B136" t="s">
+        <v>389</v>
+      </c>
+      <c r="C136" t="s">
         <v>324</v>
-      </c>
-      <c r="B136" t="s">
-        <v>391</v>
-      </c>
-      <c r="C136" t="s">
-        <v>325</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>326</v>
+      </c>
+      <c r="B137" t="s">
         <v>327</v>
-      </c>
-      <c r="B137" t="s">
-        <v>328</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -4488,52 +4504,77 @@
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B138" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C138" t="s">
+        <v>415</v>
+      </c>
+      <c r="D138" t="s">
+        <v>333</v>
+      </c>
+      <c r="F138" t="s">
         <v>417</v>
-      </c>
-      <c r="D138" t="s">
-        <v>334</v>
-      </c>
-      <c r="F138" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C140" t="s">
+        <v>515</v>
+      </c>
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
+        <v>519</v>
+      </c>
+      <c r="C141" t="s">
+        <v>518</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C141" t="s">
-        <v>520</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>523</v>
+    </row>
+    <row r="142" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>573</v>
+      </c>
+      <c r="C142" t="s">
+        <v>572</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>578</v>
+      </c>
+      <c r="C143" t="s">
+        <v>576</v>
+      </c>
+      <c r="D143" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -4553,6 +4594,8 @@
     <hyperlink ref="F117" r:id="rId8" xr:uid="{15AAE0D8-D438-0445-BD6E-A0C919093326}"/>
     <hyperlink ref="F140" r:id="rId9" xr:uid="{C764D21E-FDB9-1C48-8020-8398498CD7FB}"/>
     <hyperlink ref="F51" r:id="rId10" xr:uid="{8632FAAB-9942-C948-93C9-135910C1F7F4}"/>
+    <hyperlink ref="F142" r:id="rId11" xr:uid="{2EA298A2-CC64-B04C-960D-E1F7947248DE}"/>
+    <hyperlink ref="F91" r:id="rId12" xr:uid="{B43503AC-165A-5040-B6FB-497FB3232BAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C84761-B512-B440-B547-62374998B14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464C0249-B688-1247-B1D1-F4ACA98C9128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,9 +919,6 @@
     <t>09/06/2026</t>
   </si>
   <si>
-    <t>Happy (1972)</t>
-  </si>
-  <si>
     <t>Pharrell Williams</t>
   </si>
   <si>
@@ -1773,6 +1770,9 @@
   </si>
   <si>
     <t>Soul Makossa (1972)</t>
+  </si>
+  <si>
+    <t>Happy (2013)</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2174,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2217,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2234,16 +2234,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2251,16 +2251,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" t="s">
+        <v>407</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>409</v>
-      </c>
-      <c r="C5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2268,10 +2268,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2285,10 +2285,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2302,7 +2302,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2319,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2336,13 +2336,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2353,13 +2353,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" t="s">
         <v>334</v>
-      </c>
-      <c r="D11" t="s">
-        <v>335</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2387,16 +2387,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2424,7 +2424,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2438,7 +2438,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2455,10 +2455,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2472,10 +2472,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C18" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2506,7 +2506,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2515,7 +2515,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2523,13 +2523,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C21" t="s">
+        <v>331</v>
+      </c>
+      <c r="D21" t="s">
         <v>332</v>
-      </c>
-      <c r="D21" t="s">
-        <v>333</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2543,7 +2543,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2557,7 +2557,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2574,7 +2574,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2591,7 +2591,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2611,7 +2611,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2625,16 +2625,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2642,16 +2642,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C28" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2659,16 +2659,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C29" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2676,16 +2676,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C30" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2693,16 +2693,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2710,10 +2710,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" t="s">
         <v>338</v>
-      </c>
-      <c r="C32" t="s">
-        <v>339</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2727,16 +2727,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C33" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2744,16 +2744,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2761,10 +2761,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2778,10 +2778,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2795,16 +2795,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2812,16 +2812,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D38" t="s">
         <v>227</v>
       </c>
       <c r="F38" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2829,16 +2829,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C39" t="s">
         <v>404</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>405</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2846,10 +2846,10 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C40" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D40" t="s">
         <v>267</v>
@@ -2863,16 +2863,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2880,16 +2880,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C42" t="s">
+        <v>487</v>
+      </c>
+      <c r="D42" t="s">
         <v>488</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>489</v>
-      </c>
-      <c r="F42" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2897,7 +2897,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2914,7 +2914,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2931,16 +2931,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2954,7 +2954,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2965,16 +2965,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
+        <v>492</v>
+      </c>
+      <c r="C47" t="s">
+        <v>491</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>493</v>
-      </c>
-      <c r="C47" t="s">
-        <v>492</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2982,16 +2982,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2999,16 +2999,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C49" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3033,16 +3033,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
+        <v>558</v>
+      </c>
+      <c r="C51" t="s">
         <v>559</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3050,16 +3050,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C52" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3067,13 +3067,13 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C53" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D53" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -3084,7 +3084,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3101,16 +3101,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C55" t="s">
+        <v>496</v>
+      </c>
+      <c r="D55" t="s">
+        <v>498</v>
+      </c>
+      <c r="F55" t="s">
         <v>497</v>
-      </c>
-      <c r="D55" t="s">
-        <v>499</v>
-      </c>
-      <c r="F55" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3135,16 +3135,16 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3155,7 +3155,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -3169,16 +3169,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
+        <v>500</v>
+      </c>
+      <c r="C59" t="s">
+        <v>538</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
         <v>501</v>
-      </c>
-      <c r="C59" t="s">
-        <v>539</v>
-      </c>
-      <c r="D59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3203,16 +3203,16 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C61" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3254,16 +3254,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
+        <v>524</v>
+      </c>
+      <c r="C64" t="s">
+        <v>523</v>
+      </c>
+      <c r="D64" t="s">
         <v>525</v>
       </c>
-      <c r="C64" t="s">
-        <v>524</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
         <v>526</v>
-      </c>
-      <c r="F64" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3271,16 +3271,16 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C65" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3288,7 +3288,7 @@
         <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C66" t="s">
         <v>145</v>
@@ -3339,16 +3339,16 @@
         <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C69" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3356,16 +3356,16 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C70" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3390,7 +3390,7 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C72" t="s">
         <v>163</v>
@@ -3407,10 +3407,10 @@
         <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C73" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D73" t="s">
         <v>166</v>
@@ -3424,7 +3424,7 @@
         <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C74" t="s">
         <v>169</v>
@@ -3441,16 +3441,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C75" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3458,16 +3458,16 @@
         <v>172</v>
       </c>
       <c r="B76" t="s">
+        <v>424</v>
+      </c>
+      <c r="C76" t="s">
         <v>425</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>426</v>
       </c>
-      <c r="D76" t="s">
+      <c r="F76" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3478,7 +3478,7 @@
         <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3509,7 +3509,7 @@
         <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -3526,16 +3526,16 @@
         <v>183</v>
       </c>
       <c r="B80" t="s">
+        <v>349</v>
+      </c>
+      <c r="C80" t="s">
+        <v>348</v>
+      </c>
+      <c r="D80" t="s">
         <v>350</v>
       </c>
-      <c r="C80" t="s">
-        <v>349</v>
-      </c>
-      <c r="D80" t="s">
-        <v>351</v>
-      </c>
       <c r="F80" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3546,7 +3546,7 @@
         <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -3560,16 +3560,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C82" t="s">
+        <v>502</v>
+      </c>
+      <c r="D82" t="s">
         <v>503</v>
       </c>
-      <c r="D82" t="s">
-        <v>504</v>
-      </c>
       <c r="F82" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3577,16 +3577,16 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
+        <v>567</v>
+      </c>
+      <c r="C83" t="s">
+        <v>565</v>
+      </c>
+      <c r="D83" t="s">
+        <v>566</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="C83" t="s">
-        <v>566</v>
-      </c>
-      <c r="D83" t="s">
-        <v>567</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3594,7 +3594,7 @@
         <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C84" t="s">
         <v>191</v>
@@ -3611,13 +3611,13 @@
         <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C85" t="s">
         <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F85" t="s">
         <v>196</v>
@@ -3628,13 +3628,13 @@
         <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C86" t="s">
         <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
@@ -3645,7 +3645,7 @@
         <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
         <v>201</v>
@@ -3679,10 +3679,10 @@
         <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C89" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
@@ -3696,7 +3696,7 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C90" t="s">
         <v>210</v>
@@ -3713,16 +3713,16 @@
         <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C91" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -3730,7 +3730,7 @@
         <v>213</v>
       </c>
       <c r="B92" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C92" t="s">
         <v>214</v>
@@ -3750,7 +3750,7 @@
         <v>217</v>
       </c>
       <c r="C93" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
@@ -3764,7 +3764,7 @@
         <v>219</v>
       </c>
       <c r="B94" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C94" t="s">
         <v>220</v>
@@ -3781,10 +3781,10 @@
         <v>222</v>
       </c>
       <c r="B95" t="s">
+        <v>341</v>
+      </c>
+      <c r="C95" t="s">
         <v>342</v>
-      </c>
-      <c r="C95" t="s">
-        <v>343</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -3798,7 +3798,7 @@
         <v>225</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C96" t="s">
         <v>226</v>
@@ -3815,16 +3815,16 @@
         <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C97" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -3849,16 +3849,16 @@
         <v>234</v>
       </c>
       <c r="B99" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C99" t="s">
+        <v>397</v>
+      </c>
+      <c r="D99" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="D99" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
@@ -3866,7 +3866,7 @@
         <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C100" t="s">
         <v>131</v>
@@ -3883,7 +3883,7 @@
         <v>237</v>
       </c>
       <c r="B101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C101" t="s">
         <v>238</v>
@@ -3934,10 +3934,10 @@
         <v>247</v>
       </c>
       <c r="B104" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C104" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
@@ -3951,16 +3951,16 @@
         <v>249</v>
       </c>
       <c r="B105" t="s">
+        <v>429</v>
+      </c>
+      <c r="C105" t="s">
         <v>430</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>431</v>
       </c>
-      <c r="D105" t="s">
+      <c r="F105" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -3968,7 +3968,7 @@
         <v>250</v>
       </c>
       <c r="B106" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C106" t="s">
         <v>251</v>
@@ -3985,7 +3985,7 @@
         <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -4002,7 +4002,7 @@
         <v>255</v>
       </c>
       <c r="B108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C108" t="s">
         <v>256</v>
@@ -4022,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="C109" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -4036,10 +4036,10 @@
         <v>261</v>
       </c>
       <c r="B110" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C110" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D110" t="s">
         <v>166</v>
@@ -4056,7 +4056,7 @@
         <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -4070,16 +4070,16 @@
         <v>266</v>
       </c>
       <c r="B112" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C112" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D112" t="s">
         <v>267</v>
       </c>
       <c r="F112" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -4087,7 +4087,7 @@
         <v>268</v>
       </c>
       <c r="B113" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C113" t="s">
         <v>205</v>
@@ -4104,7 +4104,7 @@
         <v>270</v>
       </c>
       <c r="B114" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C114" t="s">
         <v>271</v>
@@ -4121,16 +4121,16 @@
         <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C115" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -4138,16 +4138,16 @@
         <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C116" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -4155,16 +4155,16 @@
         <v>275</v>
       </c>
       <c r="B117" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C117" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
@@ -4175,7 +4175,7 @@
         <v>277</v>
       </c>
       <c r="C118" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
@@ -4192,13 +4192,13 @@
         <v>280</v>
       </c>
       <c r="C119" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
@@ -4206,16 +4206,16 @@
         <v>281</v>
       </c>
       <c r="B120" t="s">
+        <v>410</v>
+      </c>
+      <c r="C120" t="s">
         <v>411</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>412</v>
       </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
         <v>413</v>
-      </c>
-      <c r="F120" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
@@ -4240,7 +4240,7 @@
         <v>286</v>
       </c>
       <c r="B122" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C122" t="s">
         <v>287</v>
@@ -4260,7 +4260,7 @@
         <v>291</v>
       </c>
       <c r="C123" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
@@ -4274,24 +4274,24 @@
         <v>293</v>
       </c>
       <c r="B124" t="s">
+        <v>578</v>
+      </c>
+      <c r="C124" t="s">
         <v>294</v>
-      </c>
-      <c r="C124" t="s">
-        <v>295</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>296</v>
+      </c>
+      <c r="B125" t="s">
         <v>297</v>
-      </c>
-      <c r="B125" t="s">
-        <v>298</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -4300,83 +4300,83 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>299</v>
+      </c>
+      <c r="B126" t="s">
         <v>300</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>301</v>
-      </c>
-      <c r="C126" t="s">
-        <v>302</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C127" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>304</v>
+      </c>
+      <c r="B128" t="s">
         <v>305</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>306</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>307</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B129" t="s">
+        <v>509</v>
+      </c>
+      <c r="C129" t="s">
+        <v>508</v>
+      </c>
+      <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" t="s">
         <v>510</v>
-      </c>
-      <c r="C129" t="s">
-        <v>509</v>
-      </c>
-      <c r="D129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>309</v>
+      </c>
+      <c r="B130" t="s">
         <v>310</v>
-      </c>
-      <c r="B130" t="s">
-        <v>311</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -4385,117 +4385,117 @@
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>312</v>
+      </c>
+      <c r="B131" t="s">
+        <v>445</v>
+      </c>
+      <c r="C131" t="s">
+        <v>479</v>
+      </c>
+      <c r="D131" t="s">
+        <v>384</v>
+      </c>
+      <c r="F131" t="s">
         <v>313</v>
-      </c>
-      <c r="B131" t="s">
-        <v>446</v>
-      </c>
-      <c r="C131" t="s">
-        <v>480</v>
-      </c>
-      <c r="D131" t="s">
-        <v>385</v>
-      </c>
-      <c r="F131" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B132" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C132" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B133" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" t="s">
+        <v>527</v>
+      </c>
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" t="s">
         <v>529</v>
-      </c>
-      <c r="C133" t="s">
-        <v>528</v>
-      </c>
-      <c r="D133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>316</v>
+      </c>
+      <c r="B134" t="s">
         <v>317</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>318</v>
-      </c>
-      <c r="C134" t="s">
-        <v>319</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>320</v>
+      </c>
+      <c r="B135" t="s">
         <v>321</v>
       </c>
-      <c r="B135" t="s">
-        <v>322</v>
-      </c>
       <c r="C135" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D135" t="s">
         <v>223</v>
       </c>
       <c r="F135" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>322</v>
+      </c>
+      <c r="B136" t="s">
+        <v>388</v>
+      </c>
+      <c r="C136" t="s">
         <v>323</v>
-      </c>
-      <c r="B136" t="s">
-        <v>389</v>
-      </c>
-      <c r="C136" t="s">
-        <v>324</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>325</v>
+      </c>
+      <c r="B137" t="s">
         <v>326</v>
-      </c>
-      <c r="B137" t="s">
-        <v>327</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -4504,77 +4504,77 @@
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B138" t="s">
+        <v>415</v>
+      </c>
+      <c r="C138" t="s">
+        <v>414</v>
+      </c>
+      <c r="D138" t="s">
+        <v>332</v>
+      </c>
+      <c r="F138" t="s">
         <v>416</v>
-      </c>
-      <c r="C138" t="s">
-        <v>415</v>
-      </c>
-      <c r="D138" t="s">
-        <v>333</v>
-      </c>
-      <c r="F138" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B140" t="s">
+        <v>515</v>
+      </c>
+      <c r="C140" t="s">
+        <v>514</v>
+      </c>
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="C140" t="s">
-        <v>515</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C141" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
+        <v>572</v>
+      </c>
+      <c r="C142" t="s">
+        <v>571</v>
+      </c>
+      <c r="D142" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="C142" t="s">
-        <v>572</v>
-      </c>
-      <c r="D142" s="3" t="s">
+      <c r="F142" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C143" t="s">
+        <v>575</v>
+      </c>
+      <c r="D143" t="s">
         <v>576</v>
-      </c>
-      <c r="D143" t="s">
-        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464C0249-B688-1247-B1D1-F4ACA98C9128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F0796-9A46-E240-9E15-B9D34E178193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1468,9 +1468,6 @@
     <t>Maurice Ravel</t>
   </si>
   <si>
-    <t>Tomaso Albinoni</t>
-  </si>
-  <si>
     <t>Jacques Offenbach</t>
   </si>
   <si>
@@ -1773,6 +1770,9 @@
   </si>
   <si>
     <t>Happy (2013)</t>
+  </si>
+  <si>
+    <t>Remo Giazotto (attribué à Tomaso Albinoni)</t>
   </si>
 </sst>
 </file>
@@ -2625,16 +2625,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C27" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2642,16 +2642,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C28" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D28" t="s">
         <v>426</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2659,16 +2659,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C29" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2676,7 +2676,7 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C30" t="s">
         <v>462</v>
@@ -2685,7 +2685,7 @@
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2693,16 +2693,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2727,16 +2727,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C33" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2744,7 +2744,7 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C34" t="s">
         <v>459</v>
@@ -2753,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2804,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2849,7 +2849,7 @@
         <v>361</v>
       </c>
       <c r="C40" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D40" t="s">
         <v>267</v>
@@ -2872,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2880,16 +2880,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C42" t="s">
+        <v>486</v>
+      </c>
+      <c r="D42" t="s">
         <v>487</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>488</v>
-      </c>
-      <c r="F42" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2965,16 +2965,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
+        <v>491</v>
+      </c>
+      <c r="C47" t="s">
+        <v>490</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>492</v>
-      </c>
-      <c r="C47" t="s">
-        <v>491</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -3008,7 +3008,7 @@
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3033,16 +3033,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
+        <v>557</v>
+      </c>
+      <c r="C51" t="s">
         <v>558</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3050,16 +3050,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C52" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3084,7 +3084,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3101,16 +3101,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C55" t="s">
+        <v>495</v>
+      </c>
+      <c r="D55" t="s">
+        <v>497</v>
+      </c>
+      <c r="F55" t="s">
         <v>496</v>
-      </c>
-      <c r="D55" t="s">
-        <v>498</v>
-      </c>
-      <c r="F55" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3144,7 +3144,7 @@
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3169,16 +3169,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C59" t="s">
+        <v>537</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
         <v>500</v>
-      </c>
-      <c r="C59" t="s">
-        <v>538</v>
-      </c>
-      <c r="D59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3212,7 +3212,7 @@
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3254,16 +3254,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
+        <v>523</v>
+      </c>
+      <c r="C64" t="s">
+        <v>522</v>
+      </c>
+      <c r="D64" t="s">
         <v>524</v>
       </c>
-      <c r="C64" t="s">
-        <v>523</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
         <v>525</v>
-      </c>
-      <c r="F64" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3280,7 +3280,7 @@
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3348,7 +3348,7 @@
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3441,16 +3441,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C75" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3560,16 +3560,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C82" t="s">
+        <v>501</v>
+      </c>
+      <c r="D82" t="s">
         <v>502</v>
       </c>
-      <c r="D82" t="s">
-        <v>503</v>
-      </c>
       <c r="F82" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3577,16 +3577,16 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
+        <v>566</v>
+      </c>
+      <c r="C83" t="s">
+        <v>564</v>
+      </c>
+      <c r="D83" t="s">
+        <v>565</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="C83" t="s">
-        <v>565</v>
-      </c>
-      <c r="D83" t="s">
-        <v>566</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3634,7 +3634,7 @@
         <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
@@ -3713,16 +3713,16 @@
         <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C91" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>431</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -3824,7 +3824,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -4079,7 +4079,7 @@
         <v>267</v>
       </c>
       <c r="F112" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -4121,16 +4121,16 @@
         <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C115" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -4138,16 +4138,16 @@
         <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C116" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -4198,7 +4198,7 @@
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
@@ -4260,7 +4260,7 @@
         <v>291</v>
       </c>
       <c r="C123" t="s">
-        <v>477</v>
+        <v>578</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
@@ -4274,7 +4274,7 @@
         <v>293</v>
       </c>
       <c r="B124" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C124" t="s">
         <v>294</v>
@@ -4328,13 +4328,13 @@
         <v>378</v>
       </c>
       <c r="C127" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
@@ -4359,16 +4359,16 @@
         <v>308</v>
       </c>
       <c r="B129" t="s">
+        <v>508</v>
+      </c>
+      <c r="C129" t="s">
+        <v>507</v>
+      </c>
+      <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" t="s">
         <v>509</v>
-      </c>
-      <c r="C129" t="s">
-        <v>508</v>
-      </c>
-      <c r="D129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
@@ -4396,7 +4396,7 @@
         <v>445</v>
       </c>
       <c r="C131" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D131" t="s">
         <v>384</v>
@@ -4410,16 +4410,16 @@
         <v>314</v>
       </c>
       <c r="B132" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C132" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
@@ -4427,16 +4427,16 @@
         <v>315</v>
       </c>
       <c r="B133" t="s">
+        <v>527</v>
+      </c>
+      <c r="C133" t="s">
+        <v>526</v>
+      </c>
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" t="s">
         <v>528</v>
-      </c>
-      <c r="C133" t="s">
-        <v>527</v>
-      </c>
-      <c r="D133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
@@ -4464,13 +4464,13 @@
         <v>321</v>
       </c>
       <c r="C135" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D135" t="s">
         <v>223</v>
       </c>
       <c r="F135" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -4526,55 +4526,55 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B140" t="s">
+        <v>514</v>
+      </c>
+      <c r="C140" t="s">
+        <v>513</v>
+      </c>
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="C140" t="s">
-        <v>514</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C141" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
+        <v>571</v>
+      </c>
+      <c r="C142" t="s">
+        <v>570</v>
+      </c>
+      <c r="D142" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C142" t="s">
-        <v>571</v>
-      </c>
-      <c r="D142" s="3" t="s">
+      <c r="F142" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C143" t="s">
+        <v>574</v>
+      </c>
+      <c r="D143" t="s">
         <v>575</v>
-      </c>
-      <c r="D143" t="s">
-        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F0796-9A46-E240-9E15-B9D34E178193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412A3E59-197D-744B-8A87-06C9CE12375D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -937,13 +937,7 @@
     <t>12/06/2026</t>
   </si>
   <si>
-    <t>Every Breath You Take (1983)</t>
-  </si>
-  <si>
     <t>The Police</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=OMOGaugKpzs</t>
   </si>
   <si>
     <t>15/06/2026</t>
@@ -1773,6 +1767,12 @@
   </si>
   <si>
     <t>Remo Giazotto (attribué à Tomaso Albinoni)</t>
+  </si>
+  <si>
+    <t>Message In A Bottle (1979)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MbXWrmQW-OE&amp;list=RDMbXWrmQW-OE&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2174,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -2217,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2234,16 +2234,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" t="s">
         <v>392</v>
-      </c>
-      <c r="C4" t="s">
-        <v>394</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2251,16 +2251,16 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>407</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2268,10 +2268,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2285,10 +2285,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2302,7 +2302,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2319,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -2336,13 +2336,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -2353,13 +2353,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2387,16 +2387,16 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2424,7 +2424,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2438,7 +2438,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -2455,10 +2455,10 @@
         <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2472,10 +2472,10 @@
         <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C18" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2506,7 +2506,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -2515,7 +2515,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2523,13 +2523,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2543,7 +2543,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2557,7 +2557,7 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -2574,7 +2574,7 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -2591,7 +2591,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2611,7 +2611,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -2625,16 +2625,16 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C27" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -2642,16 +2642,16 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C28" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D28" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -2659,16 +2659,16 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C29" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D29" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -2676,16 +2676,16 @@
         <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C30" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2693,16 +2693,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -2710,10 +2710,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C32" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2727,16 +2727,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C33" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2744,16 +2744,16 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C34" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2761,10 +2761,10 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C35" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2778,10 +2778,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -2795,16 +2795,16 @@
         <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C37" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2812,16 +2812,16 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C38" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D38" t="s">
         <v>227</v>
       </c>
       <c r="F38" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -2829,16 +2829,16 @@
         <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C39" t="s">
+        <v>402</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>403</v>
-      </c>
-      <c r="C39" t="s">
-        <v>404</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2846,10 +2846,10 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C40" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D40" t="s">
         <v>267</v>
@@ -2863,16 +2863,16 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2880,16 +2880,16 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C42" t="s">
+        <v>484</v>
+      </c>
+      <c r="D42" t="s">
+        <v>485</v>
+      </c>
+      <c r="F42" t="s">
         <v>486</v>
-      </c>
-      <c r="D42" t="s">
-        <v>487</v>
-      </c>
-      <c r="F42" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2897,7 +2897,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -2914,7 +2914,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
@@ -2931,16 +2931,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C45" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2954,7 +2954,7 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
@@ -2965,16 +2965,16 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C47" t="s">
+        <v>488</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>490</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2982,16 +2982,16 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C48" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2999,16 +2999,16 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C49" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -3033,16 +3033,16 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
+        <v>555</v>
+      </c>
+      <c r="C51" t="s">
+        <v>556</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="C51" t="s">
-        <v>558</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -3050,16 +3050,16 @@
         <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C52" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -3067,13 +3067,13 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C53" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -3084,7 +3084,7 @@
         <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -3101,16 +3101,16 @@
         <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C55" t="s">
+        <v>493</v>
+      </c>
+      <c r="D55" t="s">
         <v>495</v>
       </c>
-      <c r="D55" t="s">
-        <v>497</v>
-      </c>
       <c r="F55" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C56" t="s">
         <v>107</v>
@@ -3135,16 +3135,16 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C57" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -3155,7 +3155,7 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -3169,16 +3169,16 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C59" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -3203,16 +3203,16 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C61" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -3254,16 +3254,16 @@
         <v>142</v>
       </c>
       <c r="B64" t="s">
+        <v>521</v>
+      </c>
+      <c r="C64" t="s">
+        <v>520</v>
+      </c>
+      <c r="D64" t="s">
+        <v>522</v>
+      </c>
+      <c r="F64" t="s">
         <v>523</v>
-      </c>
-      <c r="C64" t="s">
-        <v>522</v>
-      </c>
-      <c r="D64" t="s">
-        <v>524</v>
-      </c>
-      <c r="F64" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3271,16 +3271,16 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C65" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3288,7 +3288,7 @@
         <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C66" t="s">
         <v>145</v>
@@ -3339,16 +3339,16 @@
         <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C69" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3356,16 +3356,16 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C70" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3390,7 +3390,7 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C72" t="s">
         <v>163</v>
@@ -3407,10 +3407,10 @@
         <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C73" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D73" t="s">
         <v>166</v>
@@ -3424,7 +3424,7 @@
         <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C74" t="s">
         <v>169</v>
@@ -3441,16 +3441,16 @@
         <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C75" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3458,16 +3458,16 @@
         <v>172</v>
       </c>
       <c r="B76" t="s">
+        <v>422</v>
+      </c>
+      <c r="C76" t="s">
+        <v>423</v>
+      </c>
+      <c r="D76" t="s">
         <v>424</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="D76" t="s">
-        <v>426</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3478,7 +3478,7 @@
         <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3509,7 +3509,7 @@
         <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
@@ -3526,16 +3526,16 @@
         <v>183</v>
       </c>
       <c r="B80" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C80" t="s">
+        <v>346</v>
+      </c>
+      <c r="D80" t="s">
         <v>348</v>
       </c>
-      <c r="D80" t="s">
-        <v>350</v>
-      </c>
       <c r="F80" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3546,7 +3546,7 @@
         <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -3560,16 +3560,16 @@
         <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C82" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D82" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F82" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3577,16 +3577,16 @@
         <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C83" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D83" t="s">
+        <v>563</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3594,7 +3594,7 @@
         <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C84" t="s">
         <v>191</v>
@@ -3611,13 +3611,13 @@
         <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C85" t="s">
         <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F85" t="s">
         <v>196</v>
@@ -3628,13 +3628,13 @@
         <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C86" t="s">
         <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
@@ -3645,7 +3645,7 @@
         <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C87" t="s">
         <v>201</v>
@@ -3679,10 +3679,10 @@
         <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C89" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D89" t="s">
         <v>108</v>
@@ -3696,7 +3696,7 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C90" t="s">
         <v>210</v>
@@ -3713,16 +3713,16 @@
         <v>212</v>
       </c>
       <c r="B91" t="s">
+        <v>569</v>
+      </c>
+      <c r="C91" t="s">
+        <v>568</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="C91" t="s">
-        <v>570</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -3730,7 +3730,7 @@
         <v>213</v>
       </c>
       <c r="B92" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C92" t="s">
         <v>214</v>
@@ -3750,7 +3750,7 @@
         <v>217</v>
       </c>
       <c r="C93" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D93" t="s">
         <v>108</v>
@@ -3764,7 +3764,7 @@
         <v>219</v>
       </c>
       <c r="B94" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C94" t="s">
         <v>220</v>
@@ -3781,10 +3781,10 @@
         <v>222</v>
       </c>
       <c r="B95" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C95" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -3798,7 +3798,7 @@
         <v>225</v>
       </c>
       <c r="B96" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C96" t="s">
         <v>226</v>
@@ -3815,16 +3815,16 @@
         <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C97" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -3849,16 +3849,16 @@
         <v>234</v>
       </c>
       <c r="B99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C99" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
@@ -3866,7 +3866,7 @@
         <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C100" t="s">
         <v>131</v>
@@ -3883,7 +3883,7 @@
         <v>237</v>
       </c>
       <c r="B101" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C101" t="s">
         <v>238</v>
@@ -3934,10 +3934,10 @@
         <v>247</v>
       </c>
       <c r="B104" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C104" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
@@ -3951,16 +3951,16 @@
         <v>249</v>
       </c>
       <c r="B105" t="s">
+        <v>427</v>
+      </c>
+      <c r="C105" t="s">
+        <v>428</v>
+      </c>
+      <c r="D105" t="s">
         <v>429</v>
       </c>
-      <c r="C105" t="s">
+      <c r="F105" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="D105" t="s">
-        <v>431</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -3968,7 +3968,7 @@
         <v>250</v>
       </c>
       <c r="B106" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C106" t="s">
         <v>251</v>
@@ -3985,7 +3985,7 @@
         <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C107" t="s">
         <v>107</v>
@@ -4002,7 +4002,7 @@
         <v>255</v>
       </c>
       <c r="B108" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C108" t="s">
         <v>256</v>
@@ -4022,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="C109" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -4036,10 +4036,10 @@
         <v>261</v>
       </c>
       <c r="B110" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C110" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D110" t="s">
         <v>166</v>
@@ -4056,7 +4056,7 @@
         <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -4070,16 +4070,16 @@
         <v>266</v>
       </c>
       <c r="B112" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C112" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D112" t="s">
         <v>267</v>
       </c>
       <c r="F112" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -4087,7 +4087,7 @@
         <v>268</v>
       </c>
       <c r="B113" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C113" t="s">
         <v>205</v>
@@ -4104,7 +4104,7 @@
         <v>270</v>
       </c>
       <c r="B114" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C114" t="s">
         <v>271</v>
@@ -4121,16 +4121,16 @@
         <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C115" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -4138,16 +4138,16 @@
         <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C116" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -4155,16 +4155,16 @@
         <v>275</v>
       </c>
       <c r="B117" t="s">
+        <v>431</v>
+      </c>
+      <c r="C117" t="s">
         <v>433</v>
-      </c>
-      <c r="C117" t="s">
-        <v>435</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
@@ -4175,7 +4175,7 @@
         <v>277</v>
       </c>
       <c r="C118" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
@@ -4192,13 +4192,13 @@
         <v>280</v>
       </c>
       <c r="C119" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
@@ -4206,16 +4206,16 @@
         <v>281</v>
       </c>
       <c r="B120" t="s">
+        <v>408</v>
+      </c>
+      <c r="C120" t="s">
+        <v>409</v>
+      </c>
+      <c r="D120" t="s">
         <v>410</v>
       </c>
-      <c r="C120" t="s">
+      <c r="F120" t="s">
         <v>411</v>
-      </c>
-      <c r="D120" t="s">
-        <v>412</v>
-      </c>
-      <c r="F120" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
@@ -4240,7 +4240,7 @@
         <v>286</v>
       </c>
       <c r="B122" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C122" t="s">
         <v>287</v>
@@ -4260,7 +4260,7 @@
         <v>291</v>
       </c>
       <c r="C123" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D123" t="s">
         <v>108</v>
@@ -4274,7 +4274,7 @@
         <v>293</v>
       </c>
       <c r="B124" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C124" t="s">
         <v>294</v>
@@ -4308,75 +4308,75 @@
         <v>299</v>
       </c>
       <c r="B126" t="s">
+        <v>577</v>
+      </c>
+      <c r="C126" t="s">
         <v>300</v>
-      </c>
-      <c r="C126" t="s">
-        <v>301</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
       </c>
       <c r="F126" t="s">
-        <v>302</v>
+        <v>578</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B127" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C127" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>302</v>
+      </c>
+      <c r="B128" t="s">
+        <v>303</v>
+      </c>
+      <c r="C128" t="s">
         <v>304</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>305</v>
-      </c>
-      <c r="C128" t="s">
-        <v>306</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B129" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C129" t="s">
+        <v>505</v>
+      </c>
+      <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" t="s">
         <v>507</v>
-      </c>
-      <c r="D129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B130" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -4385,117 +4385,117 @@
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B131" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C131" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D131" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B132" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C132" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B133" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C133" t="s">
+        <v>524</v>
+      </c>
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" t="s">
         <v>526</v>
-      </c>
-      <c r="D133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>314</v>
+      </c>
+      <c r="B134" t="s">
+        <v>315</v>
+      </c>
+      <c r="C134" t="s">
         <v>316</v>
-      </c>
-      <c r="B134" t="s">
-        <v>317</v>
-      </c>
-      <c r="C134" t="s">
-        <v>318</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B135" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C135" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D135" t="s">
         <v>223</v>
       </c>
       <c r="F135" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B136" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C136" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -4504,77 +4504,77 @@
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B138" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C138" t="s">
+        <v>412</v>
+      </c>
+      <c r="D138" t="s">
+        <v>330</v>
+      </c>
+      <c r="F138" t="s">
         <v>414</v>
-      </c>
-      <c r="D138" t="s">
-        <v>332</v>
-      </c>
-      <c r="F138" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B140" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C140" t="s">
+        <v>511</v>
+      </c>
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
+        <v>515</v>
+      </c>
+      <c r="C141" t="s">
+        <v>514</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="C141" t="s">
-        <v>516</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
+        <v>569</v>
+      </c>
+      <c r="C142" t="s">
+        <v>568</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="C142" t="s">
-        <v>570</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C143" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D143" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Documents/Codex/2026-08-10/referenced-chatgpt-conversation-this-is-an/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4681AB6-6E2E-D240-82D4-DB4B9E702F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221F9560-5739-0447-927D-4953D9453488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>46391</v>
+        <v>46026</v>
       </c>
       <c r="B57" t="s">
         <v>185</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>46392</v>
+        <v>46027</v>
       </c>
       <c r="B58" t="s">
         <v>188</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>46394</v>
+        <v>46029</v>
       </c>
       <c r="B59" t="s">
         <v>191</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>46395</v>
+        <v>46030</v>
       </c>
       <c r="B60" t="s">
         <v>131</v>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>46398</v>
+        <v>46033</v>
       </c>
       <c r="B61" t="s">
         <v>194</v>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>46399</v>
+        <v>46034</v>
       </c>
       <c r="B62" t="s">
         <v>196</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>46401</v>
+        <v>46036</v>
       </c>
       <c r="B63" t="s">
         <v>200</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>46402</v>
+        <v>46037</v>
       </c>
       <c r="B64" t="s">
         <v>203</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>46405</v>
+        <v>46040</v>
       </c>
       <c r="B65" t="s">
         <v>207</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>46406</v>
+        <v>46041</v>
       </c>
       <c r="B66" t="s">
         <v>209</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="B67" t="s">
         <v>213</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>46409</v>
+        <v>46044</v>
       </c>
       <c r="B68" t="s">
         <v>216</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>46412</v>
+        <v>46047</v>
       </c>
       <c r="B69" t="s">
         <v>220</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>46413</v>
+        <v>46048</v>
       </c>
       <c r="B70" t="s">
         <v>224</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>46415</v>
+        <v>46050</v>
       </c>
       <c r="B71" t="s">
         <v>227</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
-        <v>46416</v>
+        <v>46051</v>
       </c>
       <c r="B72" t="s">
         <v>230</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B73" t="s">
         <v>234</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
-        <v>46420</v>
+        <v>46055</v>
       </c>
       <c r="B74" t="s">
         <v>237</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>46422</v>
+        <v>46057</v>
       </c>
       <c r="B75" t="s">
         <v>241</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>46423</v>
+        <v>46058</v>
       </c>
       <c r="B76" t="s">
         <v>244</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>46426</v>
+        <v>46061</v>
       </c>
       <c r="B77" t="s">
         <v>247</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>46427</v>
+        <v>46062</v>
       </c>
       <c r="B78" t="s">
         <v>249</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>46429</v>
+        <v>46064</v>
       </c>
       <c r="B79" t="s">
         <v>253</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
-        <v>46430</v>
+        <v>46065</v>
       </c>
       <c r="B80" t="s">
         <v>256</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
-        <v>46433</v>
+        <v>46068</v>
       </c>
       <c r="B81" t="s">
         <v>260</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
-        <v>46434</v>
+        <v>46069</v>
       </c>
       <c r="B82" t="s">
         <v>263</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
-        <v>46436</v>
+        <v>46071</v>
       </c>
       <c r="B83" t="s">
         <v>266</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
-        <v>46437</v>
+        <v>46072</v>
       </c>
       <c r="B84" t="s">
         <v>269</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
-        <v>46454</v>
+        <v>46089</v>
       </c>
       <c r="B85" t="s">
         <v>272</v>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
-        <v>46455</v>
+        <v>46090</v>
       </c>
       <c r="B86" t="s">
         <v>112</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
-        <v>46457</v>
+        <v>46092</v>
       </c>
       <c r="B87" t="s">
         <v>276</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>46458</v>
+        <v>46093</v>
       </c>
       <c r="B88" t="s">
         <v>279</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
-        <v>46461</v>
+        <v>46096</v>
       </c>
       <c r="B89" t="s">
         <v>282</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
-        <v>46462</v>
+        <v>46097</v>
       </c>
       <c r="B90" t="s">
         <v>285</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
-        <v>46464</v>
+        <v>46099</v>
       </c>
       <c r="B91" t="s">
         <v>288</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
-        <v>46465</v>
+        <v>46100</v>
       </c>
       <c r="B92" t="s">
         <v>291</v>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>46468</v>
+        <v>46103</v>
       </c>
       <c r="B93" t="s">
         <v>294</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>46469</v>
+        <v>46104</v>
       </c>
       <c r="B94" t="s">
         <v>297</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>46471</v>
+        <v>46106</v>
       </c>
       <c r="B95" t="s">
         <v>300</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>46472</v>
+        <v>46107</v>
       </c>
       <c r="B96" t="s">
         <v>302</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>46475</v>
+        <v>46110</v>
       </c>
       <c r="B97" t="s">
         <v>305</v>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>46476</v>
+        <v>46111</v>
       </c>
       <c r="B98" t="s">
         <v>138</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>46478</v>
+        <v>46113</v>
       </c>
       <c r="B99" t="s">
         <v>308</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>46479</v>
+        <v>46114</v>
       </c>
       <c r="B100" t="s">
         <v>311</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
-        <v>46483</v>
+        <v>46118</v>
       </c>
       <c r="B101" t="s">
         <v>151</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
-        <v>46485</v>
+        <v>46120</v>
       </c>
       <c r="B102" t="s">
         <v>314</v>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
-        <v>46486</v>
+        <v>46121</v>
       </c>
       <c r="B103" t="s">
         <v>317</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
-        <v>46489</v>
+        <v>46124</v>
       </c>
       <c r="B104" t="s">
         <v>320</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
-        <v>46490</v>
+        <v>46125</v>
       </c>
       <c r="B105" t="s">
         <v>323</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
-        <v>46492</v>
+        <v>46127</v>
       </c>
       <c r="B106" t="s">
         <v>326</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
-        <v>46493</v>
+        <v>46128</v>
       </c>
       <c r="B107" t="s">
         <v>329</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
-        <v>46496</v>
+        <v>46131</v>
       </c>
       <c r="B108" t="s">
         <v>332</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
-        <v>46497</v>
+        <v>46132</v>
       </c>
       <c r="B109" t="s">
         <v>125</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
-        <v>46499</v>
+        <v>46134</v>
       </c>
       <c r="B110" t="s">
         <v>335</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
-        <v>46500</v>
+        <v>46135</v>
       </c>
       <c r="B111" t="s">
         <v>338</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
-        <v>46510</v>
+        <v>46145</v>
       </c>
       <c r="B112" t="s">
         <v>342</v>
@@ -4091,7 +4091,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
-        <v>46511</v>
+        <v>46146</v>
       </c>
       <c r="B113" t="s">
         <v>345</v>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
-        <v>46517</v>
+        <v>46152</v>
       </c>
       <c r="B114" t="s">
         <v>348</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
-        <v>46518</v>
+        <v>46153</v>
       </c>
       <c r="B115" t="s">
         <v>350</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
-        <v>46520</v>
+        <v>46155</v>
       </c>
       <c r="B116" t="s">
         <v>353</v>
@@ -4159,7 +4159,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
-        <v>46521</v>
+        <v>46156</v>
       </c>
       <c r="B117" t="s">
         <v>356</v>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
-        <v>46525</v>
+        <v>46160</v>
       </c>
       <c r="B118" t="s">
         <v>359</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
-        <v>46527</v>
+        <v>46162</v>
       </c>
       <c r="B119" t="s">
         <v>363</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
-        <v>46528</v>
+        <v>46163</v>
       </c>
       <c r="B120" t="s">
         <v>366</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
-        <v>46531</v>
+        <v>46166</v>
       </c>
       <c r="B121" t="s">
         <v>369</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
-        <v>46532</v>
+        <v>46167</v>
       </c>
       <c r="B122" t="s">
         <v>372</v>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
-        <v>46534</v>
+        <v>46169</v>
       </c>
       <c r="B123" t="s">
         <v>376</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
-        <v>46535</v>
+        <v>46170</v>
       </c>
       <c r="B124" t="s">
         <v>379</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
-        <v>46538</v>
+        <v>46173</v>
       </c>
       <c r="B125" t="s">
         <v>382</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
-        <v>46539</v>
+        <v>46174</v>
       </c>
       <c r="B126" t="s">
         <v>384</v>
@@ -4329,7 +4329,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
-        <v>46541</v>
+        <v>46176</v>
       </c>
       <c r="B127" t="s">
         <v>387</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
-        <v>46542</v>
+        <v>46177</v>
       </c>
       <c r="B128" t="s">
         <v>391</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
-        <v>46545</v>
+        <v>46180</v>
       </c>
       <c r="B129" t="s">
         <v>394</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
-        <v>46546</v>
+        <v>46181</v>
       </c>
       <c r="B130" t="s">
         <v>397</v>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
-        <v>46548</v>
+        <v>46183</v>
       </c>
       <c r="B131" t="s">
         <v>400</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
-        <v>46549</v>
+        <v>46184</v>
       </c>
       <c r="B132" t="s">
         <v>402</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
-        <v>46552</v>
+        <v>46187</v>
       </c>
       <c r="B133" t="s">
         <v>405</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
-        <v>46553</v>
+        <v>46188</v>
       </c>
       <c r="B134" t="s">
         <v>407</v>
@@ -4465,7 +4465,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
-        <v>46555</v>
+        <v>46190</v>
       </c>
       <c r="B135" t="s">
         <v>410</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
-        <v>46556</v>
+        <v>46191</v>
       </c>
       <c r="B136" t="s">
         <v>413</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
-        <v>46559</v>
+        <v>46194</v>
       </c>
       <c r="B137" t="s">
         <v>416</v>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
-        <v>46560</v>
+        <v>46195</v>
       </c>
       <c r="B138" t="s">
         <v>84</v>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
-        <v>46562</v>
+        <v>46197</v>
       </c>
       <c r="B139" t="s">
         <v>418</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
-        <v>46563</v>
+        <v>46198</v>
       </c>
       <c r="B140" t="s">
         <v>421</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
-        <v>46566</v>
+        <v>46201</v>
       </c>
       <c r="B141" t="s">
         <v>425</v>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
-        <v>46567</v>
+        <v>46202</v>
       </c>
       <c r="B142" t="s">
         <v>428</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B143" t="s">
         <v>431</v>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
-        <v>46570</v>
+        <v>46205</v>
       </c>
       <c r="B144" t="s">
         <v>433</v>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5A4C448-6424-DA4E-AE51-78478F511CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FC7E71-2A1B-AC48-8FA0-CED940FCA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="688">
   <si>
     <t>Date</t>
   </si>
@@ -180,22 +180,10 @@
     <t>https://www.youtube.com/watch?v=UEWCCSuHsuQ&amp;list=RDUEWCCSuHsuQ&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Patricia Kaas</t>
-  </si>
-  <si>
-    <t>Mademoiselle chante le blues</t>
-  </si>
-  <si>
     <t>Chanson française</t>
   </si>
   <si>
     <t>Voix, piano, orchestre</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Patricia%20Kaas%20Mademoiselle%20chante%20le%20blues</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=g17yeAGwJos</t>
   </si>
   <si>
     <t>Canada</t>
@@ -259,39 +247,18 @@
     <t>https://www.youtube.com/watch?v=JFQ1TSzdpRA&amp;list=RDJFQ1TSzdpRA&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Pomme</t>
-  </si>
-  <si>
-    <t>Grandiose</t>
-  </si>
-  <si>
     <t>Chanson / folk</t>
   </si>
   <si>
     <t>Voix, guitare, piano</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Pomme%20Grandiose</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=jIqA5sg5gZM</t>
-  </si>
-  <si>
     <t>Argentine</t>
   </si>
   <si>
-    <t>Mercedes Sosa</t>
-  </si>
-  <si>
-    <t>Gracias a la Vida</t>
-  </si>
-  <si>
     <t>Folk</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=cIrGQD84F1g&amp;list=RDcIrGQD84F1g&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>Allemagne</t>
   </si>
   <si>
@@ -496,9 +463,6 @@
     <t>Israël</t>
   </si>
   <si>
-    <t>Noa</t>
-  </si>
-  <si>
     <t>Beautiful That Way</t>
   </si>
   <si>
@@ -535,9 +499,6 @@
     <t>Royaume-Uni / Algérie</t>
   </si>
   <si>
-    <t>Sting &amp; Cheb Mami</t>
-  </si>
-  <si>
     <t>Desert Rose</t>
   </si>
   <si>
@@ -670,39 +631,9 @@
     <t>https://www.youtube.com/watch?v=2KPriDj8SYs&amp;list=RD2KPriDj8SYs&amp;start_radio=1</t>
   </si>
   <si>
-    <t>France Gall</t>
-  </si>
-  <si>
-    <t>Ella, elle l’a</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=France%20Gall%20Ella%2C%20elle%20l%E2%80%99a</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lgHGU8gqz9U</t>
-  </si>
-  <si>
-    <t>France / Belgique</t>
-  </si>
-  <si>
-    <t>Duo mixte</t>
-  </si>
-  <si>
-    <t>Renaud &amp; Axelle Red</t>
-  </si>
-  <si>
-    <t>Manhattan-Kaboul</t>
-  </si>
-  <si>
     <t>Voix, guitare, piano, batterie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Renaud%20%26%20Axelle%20Red%20Manhattan-Kaboul</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=0qeV8PDBH8E</t>
-  </si>
-  <si>
     <t>Norvège</t>
   </si>
   <si>
@@ -778,9 +709,6 @@
     <t>Ukraine</t>
   </si>
   <si>
-    <t>Estas Tonne feat. Peia</t>
-  </si>
-  <si>
     <t>Bird's Teardrops</t>
   </si>
   <si>
@@ -790,45 +718,9 @@
     <t>https://www.youtube.com/watch?v=hn10okvX19E</t>
   </si>
   <si>
-    <t>Amel Bent</t>
-  </si>
-  <si>
-    <t>Ma philosophie</t>
-  </si>
-  <si>
-    <t>Pop / soul</t>
-  </si>
-  <si>
     <t>Voix, piano, guitare</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Amel%20Bent%20Ma%20philosophie</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=D38EUIll1pM</t>
-  </si>
-  <si>
-    <t>Corée du Sud</t>
-  </si>
-  <si>
-    <t>PSY</t>
-  </si>
-  <si>
-    <t>Gangnam Style</t>
-  </si>
-  <si>
-    <t>K-pop</t>
-  </si>
-  <si>
-    <t>Voix, électronique</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Gangnam+Style+PSY</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=9bZkp7q19f0</t>
-  </si>
-  <si>
     <t>Pologne</t>
   </si>
   <si>
@@ -856,24 +748,9 @@
     <t>https://www.youtube.com/watch?v=7hoyPvEASRg&amp;list=RD7hoyPvEASRg&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Christophe</t>
-  </si>
-  <si>
-    <t>Aline</t>
-  </si>
-  <si>
     <t>Chanson / pop</t>
   </si>
   <si>
-    <t>Voix, piano, guitare, synthétiseur</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Christophe%20Aline</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=seoUs_zFI7c</t>
-  </si>
-  <si>
     <t>Algérie</t>
   </si>
   <si>
@@ -1138,18 +1015,6 @@
     <t>https://www.youtube.com/watch?v=EF1jfbYs3vk&amp;list=RDEF1jfbYs3vk&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Noir Désir</t>
-  </si>
-  <si>
-    <t>Comme elle vient</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Noir%20D%C3%A9sir%20Comme%20elle%20vient</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=9C9xlKkkeNA</t>
-  </si>
-  <si>
     <t>Mongolie</t>
   </si>
   <si>
@@ -1303,24 +1168,6 @@
     <t>https://www.youtube.com/watch?v=mlbIj2zYLqo</t>
   </si>
   <si>
-    <t>GIMS</t>
-  </si>
-  <si>
-    <t>Sapés comme jamais</t>
-  </si>
-  <si>
-    <t>Rap / pop</t>
-  </si>
-  <si>
-    <t>Voix, beat, synthétiseur</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=GIMS%20Sap%C3%A9s%20comme%20jamais</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=4bPGxLxogvw</t>
-  </si>
-  <si>
     <t>Mali</t>
   </si>
   <si>
@@ -1858,18 +1705,6 @@
     <t>https://www.youtube.com/watch?v=m94_C8Z7wLk&amp;list=RDm94_C8Z7wLk&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Grèce</t>
-  </si>
-  <si>
-    <t>Nana Mouskouri</t>
-  </si>
-  <si>
-    <t>Quand tu chantes</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=b6Ztw1PNvoQ&amp;list=RDb6Ztw1PNvoQ&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>Johannes Brahms</t>
   </si>
   <si>
@@ -2135,6 +1970,128 @@
   </si>
   <si>
     <t>Genres distincts</t>
+  </si>
+  <si>
+    <t>Lisa Leblanc</t>
+  </si>
+  <si>
+    <t>Pourquoi faire aujourd'hui</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RCCmgc9cZVc</t>
+  </si>
+  <si>
+    <t>Oldelaf</t>
+  </si>
+  <si>
+    <t>Les mains froides</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FwaVegAzT84&amp;list=RDFwaVegAzT84&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Wintergatan</t>
+  </si>
+  <si>
+    <t>Suède</t>
+  </si>
+  <si>
+    <t>Proof of Concept</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=m1F7Vl2szd4&amp;list=RDm1F7Vl2szd4&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Achinoam Nini</t>
+  </si>
+  <si>
+    <t>Sting</t>
+  </si>
+  <si>
+    <t>Sanseverino</t>
+  </si>
+  <si>
+    <t>Maigrir</t>
+  </si>
+  <si>
+    <t>Jazz Manouche</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VizjETIFsjs</t>
+  </si>
+  <si>
+    <t>Boney M.</t>
+  </si>
+  <si>
+    <t>Daddy Cool</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FYGTT7YhywA</t>
+  </si>
+  <si>
+    <t>Estas Tonne</t>
+  </si>
+  <si>
+    <t>Chanson Pour Les Amis</t>
+  </si>
+  <si>
+    <t>Miossec</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wwG_F5Ct4e4&amp;list=RDwwG_F5Ct4e4&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>The Michael Zager Band</t>
+  </si>
+  <si>
+    <t>Let's All Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PmzxG9kdZhM&amp;list=RDPmzxG9kdZhM&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Le lion est mort ce soir</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xb3mhXCsBJg&amp;list=RDxb3mhXCsBJg&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Jardin d'hiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Henri Salvador</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lNZIzor29LI&amp;list=RDlNZIzor29LI&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Cerrone</t>
+  </si>
+  <si>
+    <t>Supernature</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OPsPmi35OeY&amp;list=RDOPsPmi35OeY&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Lucky Chops</t>
+  </si>
+  <si>
+    <t>Danza</t>
+  </si>
+  <si>
+    <t>Fanfare</t>
+  </si>
+  <si>
+    <t>Cuivres, Vent</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ddijvwAMw0o&amp;list=RDddijvwAMw0o&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Pow Wow (groupe)</t>
   </si>
 </sst>
 </file>
@@ -2732,39 +2689,37 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46275</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3">
-        <v>1987</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>55</v>
+        <v>650</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>56</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2775,31 +2730,31 @@
         <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3">
         <v>2019</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K8" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2810,7 +2765,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3">
         <v>1962</v>
@@ -2819,22 +2774,22 @@
         <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2851,25 +2806,25 @@
         <v>1986</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2883,28 +2838,26 @@
         <v>21</v>
       </c>
       <c r="D11" s="3">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>651</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>652</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>653</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>82</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2912,34 +2865,32 @@
         <v>46283</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="D12" s="3">
-        <v>1971</v>
+        <v>2019</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>654</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>85</v>
+        <v>656</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>87</v>
+        <v>657</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>87</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -2950,7 +2901,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3">
         <v>1761</v>
@@ -2959,22 +2910,22 @@
         <v>37</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2985,7 +2936,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3">
         <v>2000</v>
@@ -2994,22 +2945,22 @@
         <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3026,25 +2977,25 @@
         <v>1998</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3052,34 +3003,34 @@
         <v>46290</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3">
         <v>2014</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3090,7 +3041,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D17" s="3">
         <v>1786</v>
@@ -3099,22 +3050,22 @@
         <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3122,10 +3073,10 @@
         <v>46294</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3">
         <v>2007</v>
@@ -3134,22 +3085,22 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3169,22 +3120,22 @@
         <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3192,10 +3143,10 @@
         <v>46297</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D20" s="3">
         <v>2015</v>
@@ -3204,22 +3155,22 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3239,22 +3190,22 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3262,34 +3213,34 @@
         <v>46301</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D22" s="3">
         <v>1998</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3309,22 +3260,22 @@
         <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3335,7 +3286,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3">
         <v>1999</v>
@@ -3344,22 +3295,22 @@
         <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>156</v>
+        <v>658</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3370,7 +3321,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D25" s="3">
         <v>1853</v>
@@ -3379,22 +3330,22 @@
         <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3402,34 +3353,34 @@
         <v>46308</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D26" s="3">
         <v>2000</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>659</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3446,25 +3397,25 @@
         <v>2002</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3472,34 +3423,34 @@
         <v>46311</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D28" s="3">
         <v>1994</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3510,7 +3461,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D29" s="3">
         <v>1915</v>
@@ -3519,10 +3470,10 @@
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>40</v>
@@ -3531,10 +3482,10 @@
         <v>41</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3545,7 +3496,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D30" s="3">
         <v>1990</v>
@@ -3554,22 +3505,22 @@
         <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3586,25 +3537,25 @@
         <v>2009</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3624,22 +3575,22 @@
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3650,7 +3601,7 @@
         <v>20</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D33" s="3">
         <v>1725</v>
@@ -3659,22 +3610,22 @@
         <v>37</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3685,7 +3636,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3">
         <v>1999</v>
@@ -3694,25 +3645,25 @@
         <v>37</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>46338</v>
       </c>
@@ -3723,31 +3674,31 @@
         <v>21</v>
       </c>
       <c r="D35" s="3">
-        <v>1987</v>
+        <v>2002</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>660</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>215</v>
+        <v>661</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>97</v>
+        <v>662</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>663</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>46339</v>
       </c>
@@ -3755,31 +3706,31 @@
         <v>20</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3">
-        <v>2002</v>
+        <v>1976</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>219</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>220</v>
+        <v>664</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>221</v>
+        <v>665</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>223</v>
+        <v>666</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>224</v>
+        <v>666</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3790,7 +3741,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="D37" s="3">
         <v>1875</v>
@@ -3799,22 +3750,22 @@
         <v>37</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3834,22 +3785,22 @@
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3866,25 +3817,25 @@
         <v>2014</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3895,7 +3846,7 @@
         <v>35</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="D40" s="3">
         <v>2013</v>
@@ -3904,22 +3855,22 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3939,22 +3890,22 @@
         <v>37</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -3965,31 +3916,31 @@
         <v>20</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="D42" s="3">
         <v>2018</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>250</v>
+        <v>667</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4003,28 +3954,26 @@
         <v>21</v>
       </c>
       <c r="D43" s="3">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>254</v>
+        <v>669</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>255</v>
+        <v>668</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>259</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4035,31 +3984,29 @@
         <v>43</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2012</v>
+        <v>1978</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>261</v>
+        <v>671</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>262</v>
+        <v>672</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>264</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>265</v>
+        <v>673</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>266</v>
+        <v>673</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4070,7 +4017,7 @@
         <v>20</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D45" s="3">
         <v>1834</v>
@@ -4079,22 +4026,22 @@
         <v>37</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4105,7 +4052,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D46" s="3">
         <v>1988</v>
@@ -4114,22 +4061,22 @@
         <v>37</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4143,28 +4090,28 @@
         <v>21</v>
       </c>
       <c r="D47" s="3">
-        <v>1965</v>
+        <v>1992</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>276</v>
+        <v>687</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>277</v>
+        <v>674</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>279</v>
+        <v>70</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>280</v>
+        <v>675</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>281</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4175,31 +4122,31 @@
         <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="D48" s="3">
         <v>1993</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4210,7 +4157,7 @@
         <v>20</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D49" s="3">
         <v>1876</v>
@@ -4219,22 +4166,22 @@
         <v>37</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4242,10 +4189,10 @@
         <v>46364</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D50" s="3">
         <v>2011</v>
@@ -4254,22 +4201,22 @@
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4286,25 +4233,25 @@
         <v>1982</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4312,10 +4259,10 @@
         <v>46367</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D52" s="3">
         <v>2013</v>
@@ -4324,22 +4271,22 @@
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4350,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D53" s="3">
         <v>1741</v>
@@ -4359,22 +4306,22 @@
         <v>37</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4385,7 +4332,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="D54" s="3">
         <v>1993</v>
@@ -4394,22 +4341,22 @@
         <v>13</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4429,22 +4376,22 @@
         <v>37</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4461,25 +4408,25 @@
         <v>1984</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4490,7 +4437,7 @@
         <v>20</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D57" s="3">
         <v>1926</v>
@@ -4499,22 +4446,22 @@
         <v>37</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4525,7 +4472,7 @@
         <v>43</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D58" s="3">
         <v>2005</v>
@@ -4534,22 +4481,22 @@
         <v>13</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>332</v>
+        <v>291</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4566,25 +4513,25 @@
         <v>1960</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>338</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4601,25 +4548,25 @@
         <v>1988</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4630,7 +4577,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="D61" s="3">
         <v>1893</v>
@@ -4639,22 +4586,22 @@
         <v>37</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4665,7 +4612,7 @@
         <v>27</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="D62" s="3">
         <v>1972</v>
@@ -4674,22 +4621,22 @@
         <v>37</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4709,22 +4656,22 @@
         <v>13</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4735,7 +4682,7 @@
         <v>27</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="D64" s="3">
         <v>1986</v>
@@ -4744,22 +4691,22 @@
         <v>37</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>362</v>
+        <v>321</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4770,7 +4717,7 @@
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D65" s="3">
         <v>1788</v>
@@ -4779,22 +4726,22 @@
         <v>37</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4811,25 +4758,25 @@
         <v>1998</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4843,28 +4790,28 @@
         <v>21</v>
       </c>
       <c r="D67" s="3">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>370</v>
+        <v>677</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>371</v>
+        <v>676</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>372</v>
+        <v>678</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>373</v>
+        <v>678</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4875,7 +4822,7 @@
         <v>43</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="D68" s="3">
         <v>2014</v>
@@ -4884,22 +4831,22 @@
         <v>37</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4919,10 +4866,10 @@
         <v>37</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>40</v>
@@ -4931,10 +4878,10 @@
         <v>41</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4945,31 +4892,31 @@
         <v>20</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D70" s="3">
         <v>1978</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>390</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4989,22 +4936,22 @@
         <v>37</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5024,10 +4971,10 @@
         <v>13</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>16</v>
@@ -5036,10 +4983,10 @@
         <v>25</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5050,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D73" s="3">
         <v>1892</v>
@@ -5059,22 +5006,22 @@
         <v>37</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5085,7 +5032,7 @@
         <v>27</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="D74" s="3">
         <v>1974</v>
@@ -5094,22 +5041,22 @@
         <v>37</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5126,25 +5073,25 @@
         <v>1955</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5152,10 +5099,10 @@
         <v>46423</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D76" s="3">
         <v>2013</v>
@@ -5164,22 +5111,22 @@
         <v>37</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>413</v>
+        <v>368</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5190,7 +5137,7 @@
         <v>20</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D77" s="3">
         <v>1725</v>
@@ -5199,22 +5146,22 @@
         <v>37</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5228,28 +5175,26 @@
         <v>21</v>
       </c>
       <c r="D78" s="3">
-        <v>2020</v>
+        <v>1977</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>421</v>
+        <v>679</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>422</v>
+        <v>680</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>423</v>
+        <v>681</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>424</v>
+        <v>681</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5263,28 +5208,28 @@
         <v>21</v>
       </c>
       <c r="D79" s="3">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>427</v>
+        <v>51</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>428</v>
+        <v>74</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5295,31 +5240,31 @@
         <v>27</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D80" s="3">
         <v>2017</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5330,7 +5275,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D81" s="3">
         <v>1808</v>
@@ -5339,22 +5284,22 @@
         <v>37</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5371,25 +5316,25 @@
         <v>1966</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5406,25 +5351,25 @@
         <v>1997</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5435,7 +5380,7 @@
         <v>35</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D84" s="3">
         <v>1995</v>
@@ -5444,22 +5389,22 @@
         <v>13</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5479,22 +5424,22 @@
         <v>37</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5505,7 +5450,7 @@
         <v>43</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D86" s="3">
         <v>1998</v>
@@ -5514,22 +5459,22 @@
         <v>13</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>455</v>
+        <v>404</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>456</v>
+        <v>405</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>457</v>
+        <v>406</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5549,22 +5494,22 @@
         <v>37</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5575,7 +5520,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="D88" s="3">
         <v>2005</v>
@@ -5584,10 +5529,10 @@
         <v>37</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>24</v>
@@ -5596,10 +5541,10 @@
         <v>17</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5610,7 +5555,7 @@
         <v>20</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D89" s="3">
         <v>1825</v>
@@ -5619,22 +5564,22 @@
         <v>37</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5654,22 +5599,22 @@
         <v>37</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5689,22 +5634,22 @@
         <v>13</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>478</v>
+        <v>427</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5715,31 +5660,31 @@
         <v>20</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D92" s="3">
         <v>1977</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>485</v>
+        <v>434</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5750,7 +5695,7 @@
         <v>20</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D93" s="3">
         <v>1888</v>
@@ -5759,22 +5704,22 @@
         <v>37</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>487</v>
+        <v>436</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5785,7 +5730,7 @@
         <v>27</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D94" s="3">
         <v>2021</v>
@@ -5794,22 +5739,22 @@
         <v>37</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>490</v>
+        <v>439</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5826,25 +5771,25 @@
         <v>2017</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>496</v>
+        <v>445</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5855,7 +5800,7 @@
         <v>43</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D96" s="3">
         <v>2008</v>
@@ -5864,22 +5809,22 @@
         <v>37</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>499</v>
+        <v>448</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5890,7 +5835,7 @@
         <v>20</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D97" s="3">
         <v>1723</v>
@@ -5899,22 +5844,22 @@
         <v>37</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>504</v>
+        <v>453</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5925,7 +5870,7 @@
         <v>20</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D98" s="3">
         <v>2025</v>
@@ -5934,10 +5879,10 @@
         <v>13</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>506</v>
+        <v>455</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>507</v>
+        <v>456</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>31</v>
@@ -5946,10 +5891,10 @@
         <v>32</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5969,10 +5914,10 @@
         <v>37</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>24</v>
@@ -5981,10 +5926,10 @@
         <v>17</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6004,22 +5949,22 @@
         <v>13</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>512</v>
+        <v>461</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>513</v>
+        <v>462</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>514</v>
+        <v>463</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6036,25 +5981,25 @@
         <v>1963</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>518</v>
+        <v>467</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>519</v>
+        <v>468</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>520</v>
+        <v>469</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6074,22 +6019,22 @@
         <v>13</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>521</v>
+        <v>470</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>522</v>
+        <v>471</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>523</v>
+        <v>472</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>524</v>
+        <v>473</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6100,31 +6045,31 @@
         <v>35</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>525</v>
+        <v>474</v>
       </c>
       <c r="D103" s="3">
         <v>1997</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>526</v>
+        <v>475</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>527</v>
+        <v>476</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>528</v>
+        <v>477</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>529</v>
+        <v>478</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>530</v>
+        <v>479</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -6135,7 +6080,7 @@
         <v>20</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D104" s="3">
         <v>1791</v>
@@ -6144,22 +6089,22 @@
         <v>37</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>532</v>
+        <v>481</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>533</v>
+        <v>482</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6170,7 +6115,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D105" s="3">
         <v>1985</v>
@@ -6179,22 +6124,22 @@
         <v>37</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>534</v>
+        <v>483</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>535</v>
+        <v>484</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>537</v>
+        <v>486</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6211,25 +6156,25 @@
         <v>2003</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>541</v>
+        <v>490</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>542</v>
+        <v>491</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6237,10 +6182,10 @@
         <v>46493</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D107" s="3">
         <v>2004</v>
@@ -6249,22 +6194,22 @@
         <v>37</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>546</v>
+        <v>495</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>547</v>
+        <v>496</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>547</v>
+        <v>496</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6275,7 +6220,7 @@
         <v>20</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D108" s="3">
         <v>1839</v>
@@ -6284,22 +6229,22 @@
         <v>37</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6310,31 +6255,31 @@
         <v>20</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D109" s="3">
         <v>1985</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>552</v>
+        <v>501</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>553</v>
+        <v>502</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6345,7 +6290,7 @@
         <v>20</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D110" s="3">
         <v>1843</v>
@@ -6354,22 +6299,22 @@
         <v>37</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>555</v>
+        <v>504</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6380,7 +6325,7 @@
         <v>20</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="D111" s="3">
         <v>2019</v>
@@ -6389,22 +6334,22 @@
         <v>13</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>558</v>
+        <v>507</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>559</v>
+        <v>508</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>560</v>
+        <v>509</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>561</v>
+        <v>510</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6424,22 +6369,22 @@
         <v>37</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>562</v>
+        <v>511</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>563</v>
+        <v>512</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>564</v>
+        <v>513</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6450,7 +6395,7 @@
         <v>20</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>565</v>
+        <v>514</v>
       </c>
       <c r="D113" s="3">
         <v>1997</v>
@@ -6459,22 +6404,22 @@
         <v>13</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>566</v>
+        <v>515</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>569</v>
+        <v>518</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>570</v>
+        <v>519</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>571</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6491,25 +6436,25 @@
         <v>1981</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6529,22 +6474,22 @@
         <v>13</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>575</v>
+        <v>524</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>576</v>
+        <v>525</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>578</v>
+        <v>527</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>579</v>
+        <v>528</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6555,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D116" s="3">
         <v>1974</v>
@@ -6564,22 +6509,22 @@
         <v>37</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>580</v>
+        <v>529</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>582</v>
+        <v>531</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>583</v>
+        <v>532</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>584</v>
+        <v>533</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6590,7 +6535,7 @@
         <v>20</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D117" s="3">
         <v>1869</v>
@@ -6599,22 +6544,22 @@
         <v>37</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>586</v>
+        <v>535</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>587</v>
+        <v>536</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>587</v>
+        <v>536</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6625,7 +6570,7 @@
         <v>43</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D118" s="3">
         <v>1983</v>
@@ -6634,22 +6579,22 @@
         <v>37</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>588</v>
+        <v>537</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>589</v>
+        <v>538</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>590</v>
+        <v>539</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6666,25 +6611,25 @@
         <v>2007</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>591</v>
+        <v>540</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>592</v>
+        <v>541</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>594</v>
+        <v>543</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6701,25 +6646,25 @@
         <v>2012</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>595</v>
+        <v>544</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>597</v>
+        <v>546</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>598</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6739,22 +6684,22 @@
         <v>37</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>600</v>
+        <v>549</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6765,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D122" s="3">
         <v>2013</v>
@@ -6774,22 +6719,22 @@
         <v>37</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>603</v>
+        <v>552</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>605</v>
+        <v>554</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6809,22 +6754,22 @@
         <v>13</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>606</v>
+        <v>555</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>608</v>
+        <v>557</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>609</v>
+        <v>558</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>609</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6835,31 +6780,31 @@
         <v>20</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>610</v>
+        <v>231</v>
       </c>
       <c r="D124" s="3">
-        <v>1975</v>
+        <v>2001</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6870,7 +6815,7 @@
         <v>20</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D125" s="3">
         <v>1868</v>
@@ -6879,22 +6824,22 @@
         <v>37</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>614</v>
+        <v>559</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>615</v>
+        <v>560</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>616</v>
+        <v>561</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>617</v>
+        <v>562</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>617</v>
+        <v>562</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6914,22 +6859,22 @@
         <v>13</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>618</v>
+        <v>563</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>619</v>
+        <v>564</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>620</v>
+        <v>565</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>622</v>
+        <v>567</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6949,22 +6894,22 @@
         <v>37</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6972,10 +6917,10 @@
         <v>46549</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D128" s="3">
         <v>2013</v>
@@ -6984,22 +6929,22 @@
         <v>37</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>625</v>
+        <v>570</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>627</v>
+        <v>572</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>628</v>
+        <v>573</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>628</v>
+        <v>573</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -7019,22 +6964,22 @@
         <v>37</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>629</v>
+        <v>574</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>630</v>
+        <v>575</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>631</v>
+        <v>576</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>632</v>
+        <v>577</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7045,7 +6990,7 @@
         <v>20</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3">
         <v>1973</v>
@@ -7054,22 +6999,22 @@
         <v>37</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>633</v>
+        <v>578</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>634</v>
+        <v>579</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>635</v>
+        <v>580</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>636</v>
+        <v>581</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>637</v>
+        <v>582</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7086,25 +7031,25 @@
         <v>2006</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>639</v>
+        <v>584</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7121,13 +7066,13 @@
         <v>1958</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>641</v>
+        <v>586</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>642</v>
+        <v>587</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>16</v>
@@ -7136,10 +7081,10 @@
         <v>17</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>643</v>
+        <v>588</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>643</v>
+        <v>588</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7159,22 +7104,22 @@
         <v>37</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>644</v>
+        <v>589</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>645</v>
+        <v>590</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>646</v>
+        <v>591</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>647</v>
+        <v>592</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7194,22 +7139,22 @@
         <v>13</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>648</v>
+        <v>593</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>649</v>
+        <v>594</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>652</v>
+        <v>597</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7229,22 +7174,22 @@
         <v>13</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>653</v>
+        <v>598</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>654</v>
+        <v>599</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>655</v>
+        <v>600</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>656</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7264,22 +7209,22 @@
         <v>13</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>659</v>
+        <v>604</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>660</v>
+        <v>605</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>660</v>
+        <v>605</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -7290,7 +7235,7 @@
         <v>20</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D137" s="3">
         <v>1824</v>
@@ -7299,22 +7244,22 @@
         <v>37</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>661</v>
+        <v>606</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>662</v>
+        <v>607</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>663</v>
+        <v>608</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>664</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7325,31 +7270,31 @@
         <v>20</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D138" s="3">
         <v>1996</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>665</v>
+        <v>610</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>666</v>
+        <v>611</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>667</v>
+        <v>612</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>669</v>
+        <v>614</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7366,25 +7311,25 @@
         <v>2003</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>670</v>
+        <v>615</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>671</v>
+        <v>616</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>672</v>
+        <v>617</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7392,34 +7337,34 @@
         <v>46570</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="D140" s="3">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>182</v>
+        <v>684</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7449,16 +7394,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>678</v>
+        <v>623</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>681</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -7548,7 +7493,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7565,7 +7510,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7582,7 +7527,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7599,7 +7544,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7616,7 +7561,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -7647,47 +7592,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>682</v>
+        <v>627</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>683</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>684</v>
+        <v>629</v>
       </c>
       <c r="B2" t="s">
-        <v>685</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>686</v>
+        <v>631</v>
       </c>
       <c r="B3" t="s">
-        <v>687</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>688</v>
+        <v>633</v>
       </c>
       <c r="B4" t="s">
-        <v>689</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>690</v>
+        <v>635</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>692</v>
+        <v>637</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7695,23 +7640,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>693</v>
+        <v>638</v>
       </c>
       <c r="B7" t="s">
-        <v>694</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>695</v>
+        <v>640</v>
       </c>
       <c r="B8" t="s">
-        <v>696</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>697</v>
+        <v>642</v>
       </c>
       <c r="B9">
         <v>139</v>
@@ -7719,7 +7664,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>698</v>
+        <v>643</v>
       </c>
       <c r="B10">
         <v>33</v>
@@ -7727,7 +7672,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>699</v>
+        <v>644</v>
       </c>
       <c r="B11">
         <v>36</v>
@@ -7735,7 +7680,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>700</v>
+        <v>645</v>
       </c>
       <c r="B12">
         <v>35</v>
@@ -7743,7 +7688,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>701</v>
+        <v>646</v>
       </c>
       <c r="B13">
         <v>35</v>
@@ -7751,7 +7696,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>678</v>
+        <v>623</v>
       </c>
       <c r="B14">
         <v>64</v>
@@ -7759,7 +7704,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="B15">
         <v>36</v>
@@ -7767,7 +7712,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="B16">
         <v>39</v>
@@ -7775,7 +7720,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>702</v>
+        <v>647</v>
       </c>
       <c r="B17">
         <v>57</v>
